--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18446,7 +18446,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-09-01 a 2026-09-15)</t>
+    <t>Ventas (2026-09-01 a 2026-09-16)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -19951,7 +19951,7 @@
         <v>61</v>
       </c>
       <c r="E65">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -22382,7 +22382,7 @@
         <v>423</v>
       </c>
       <c r="E208">
-        <v>198</v>
+        <v>129</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -22399,7 +22399,7 @@
         <v>423</v>
       </c>
       <c r="E209">
-        <v>192</v>
+        <v>144</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -22433,7 +22433,7 @@
         <v>198</v>
       </c>
       <c r="E211">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -22450,7 +22450,7 @@
         <v>198</v>
       </c>
       <c r="E212">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -22467,7 +22467,7 @@
         <v>198</v>
       </c>
       <c r="E213">
-        <v>80</v>
+        <v>56</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -25901,7 +25901,7 @@
         <v>18</v>
       </c>
       <c r="E415">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
@@ -25969,7 +25969,7 @@
         <v>18</v>
       </c>
       <c r="E419">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -27975,7 +27975,7 @@
         <v>423</v>
       </c>
       <c r="E537">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -28604,7 +28604,7 @@
         <v>61</v>
       </c>
       <c r="E574">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -29250,7 +29250,7 @@
         <v>8</v>
       </c>
       <c r="E612">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
@@ -29386,7 +29386,7 @@
         <v>423</v>
       </c>
       <c r="E620">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
@@ -29505,7 +29505,7 @@
         <v>423</v>
       </c>
       <c r="E627">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
@@ -29522,7 +29522,7 @@
         <v>423</v>
       </c>
       <c r="E628">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -29539,7 +29539,7 @@
         <v>423</v>
       </c>
       <c r="E629">
-        <v>357</v>
+        <v>333</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
@@ -29556,7 +29556,7 @@
         <v>423</v>
       </c>
       <c r="E630">
-        <v>337</v>
+        <v>320</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -29590,7 +29590,7 @@
         <v>423</v>
       </c>
       <c r="E632">
-        <v>188</v>
+        <v>158</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -29607,7 +29607,7 @@
         <v>423</v>
       </c>
       <c r="E633">
-        <v>160</v>
+        <v>122</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -29879,7 +29879,7 @@
         <v>18</v>
       </c>
       <c r="E649">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -30168,7 +30168,7 @@
         <v>423</v>
       </c>
       <c r="E666">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
@@ -30525,7 +30525,7 @@
         <v>18</v>
       </c>
       <c r="E687">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
@@ -31137,7 +31137,7 @@
         <v>18</v>
       </c>
       <c r="E723">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
@@ -31936,7 +31936,7 @@
         <v>18</v>
       </c>
       <c r="E770">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.25">
@@ -32123,7 +32123,7 @@
         <v>85</v>
       </c>
       <c r="E781">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="782" spans="1:5" x14ac:dyDescent="0.25">
@@ -33279,7 +33279,7 @@
         <v>8</v>
       </c>
       <c r="E849">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.25">
@@ -33772,7 +33772,7 @@
         <v>41</v>
       </c>
       <c r="E878">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="879" spans="1:5" x14ac:dyDescent="0.25">
@@ -34775,7 +34775,7 @@
         <v>85</v>
       </c>
       <c r="E937">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="938" spans="1:5" x14ac:dyDescent="0.25">
@@ -34877,7 +34877,7 @@
         <v>41</v>
       </c>
       <c r="E943">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="944" spans="1:5" x14ac:dyDescent="0.25">
@@ -37257,7 +37257,7 @@
         <v>18</v>
       </c>
       <c r="E1083">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
@@ -37648,7 +37648,7 @@
         <v>93</v>
       </c>
       <c r="E1106">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1107" spans="1:5" x14ac:dyDescent="0.25">
@@ -38566,7 +38566,7 @@
         <v>8</v>
       </c>
       <c r="E1160">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1161" spans="1:5" x14ac:dyDescent="0.25">
@@ -43054,7 +43054,7 @@
         <v>18</v>
       </c>
       <c r="E1424">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1425" spans="1:5" x14ac:dyDescent="0.25">
@@ -49191,7 +49191,7 @@
         <v>61</v>
       </c>
       <c r="E1785">
-        <v>71</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1786" spans="1:5" x14ac:dyDescent="0.25">
@@ -49956,7 +49956,7 @@
         <v>18</v>
       </c>
       <c r="E1830">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1831" spans="1:5" x14ac:dyDescent="0.25">
@@ -51027,7 +51027,7 @@
         <v>61</v>
       </c>
       <c r="E1893">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1894" spans="1:5" x14ac:dyDescent="0.25">
@@ -52166,7 +52166,7 @@
         <v>423</v>
       </c>
       <c r="E1960">
-        <v>736</v>
+        <v>699</v>
       </c>
     </row>
     <row r="1961" spans="1:5" x14ac:dyDescent="0.25">
@@ -52489,7 +52489,7 @@
         <v>423</v>
       </c>
       <c r="E1979">
-        <v>626</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1980" spans="1:5" x14ac:dyDescent="0.25">
@@ -59408,7 +59408,7 @@
         <v>88</v>
       </c>
       <c r="E2386">
-        <v>119</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2387" spans="1:5" x14ac:dyDescent="0.25">
@@ -61652,7 +61652,7 @@
         <v>18</v>
       </c>
       <c r="E2518">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2519" spans="1:5" x14ac:dyDescent="0.25">
@@ -61669,7 +61669,7 @@
         <v>18</v>
       </c>
       <c r="E2519">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2520" spans="1:5" x14ac:dyDescent="0.25">
@@ -62264,7 +62264,7 @@
         <v>8</v>
       </c>
       <c r="E2554">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2555" spans="1:5" x14ac:dyDescent="0.25">
@@ -62774,7 +62774,7 @@
         <v>8</v>
       </c>
       <c r="E2584">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2585" spans="1:5" x14ac:dyDescent="0.25">
@@ -62842,7 +62842,7 @@
         <v>88</v>
       </c>
       <c r="E2588">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2589" spans="1:5" x14ac:dyDescent="0.25">
@@ -65800,7 +65800,7 @@
         <v>8</v>
       </c>
       <c r="E2762">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2763" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18452,7 +18452,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-09-01 a 2026-09-22)</t>
+    <t>Ventas (2026-09-01 a 2026-09-23)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -19940,7 +19940,7 @@
         <v>41</v>
       </c>
       <c r="E64">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -20399,7 +20399,7 @@
         <v>8</v>
       </c>
       <c r="E91">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -22371,7 +22371,7 @@
         <v>423</v>
       </c>
       <c r="E207">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -22388,7 +22388,7 @@
         <v>423</v>
       </c>
       <c r="E208">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -22405,7 +22405,7 @@
         <v>423</v>
       </c>
       <c r="E209">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -25975,7 +25975,7 @@
         <v>18</v>
       </c>
       <c r="E419">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -26043,7 +26043,7 @@
         <v>61</v>
       </c>
       <c r="E423">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
@@ -28610,7 +28610,7 @@
         <v>61</v>
       </c>
       <c r="E574">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -29834,7 +29834,7 @@
         <v>13</v>
       </c>
       <c r="E646">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -31143,7 +31143,7 @@
         <v>18</v>
       </c>
       <c r="E723">
-        <v>133</v>
+        <v>97</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
@@ -32979,7 +32979,7 @@
         <v>8</v>
       </c>
       <c r="E831">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.25">
@@ -33557,7 +33557,7 @@
         <v>61</v>
       </c>
       <c r="E865">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="866" spans="1:5" x14ac:dyDescent="0.25">
@@ -33642,7 +33642,7 @@
         <v>61</v>
       </c>
       <c r="E870">
-        <v>132</v>
+        <v>72</v>
       </c>
     </row>
     <row r="871" spans="1:5" x14ac:dyDescent="0.25">
@@ -33795,7 +33795,7 @@
         <v>8</v>
       </c>
       <c r="E879">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="880" spans="1:5" x14ac:dyDescent="0.25">
@@ -34424,7 +34424,7 @@
         <v>8</v>
       </c>
       <c r="E916">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="917" spans="1:5" x14ac:dyDescent="0.25">
@@ -34900,7 +34900,7 @@
         <v>61</v>
       </c>
       <c r="E944">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="945" spans="1:5" x14ac:dyDescent="0.25">
@@ -35461,7 +35461,7 @@
         <v>423</v>
       </c>
       <c r="E977">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="978" spans="1:5" x14ac:dyDescent="0.25">
@@ -35478,7 +35478,7 @@
         <v>423</v>
       </c>
       <c r="E978">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="979" spans="1:5" x14ac:dyDescent="0.25">
@@ -43060,7 +43060,7 @@
         <v>18</v>
       </c>
       <c r="E1424">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1425" spans="1:5" x14ac:dyDescent="0.25">
@@ -49197,7 +49197,7 @@
         <v>61</v>
       </c>
       <c r="E1785">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1786" spans="1:5" x14ac:dyDescent="0.25">
@@ -51339,7 +51339,7 @@
         <v>61</v>
       </c>
       <c r="E1911">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1912" spans="1:5" x14ac:dyDescent="0.25">
@@ -51713,7 +51713,7 @@
         <v>61</v>
       </c>
       <c r="E1933">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1934" spans="1:5" x14ac:dyDescent="0.25">
@@ -52172,7 +52172,7 @@
         <v>423</v>
       </c>
       <c r="E1960">
-        <v>415</v>
+        <v>355</v>
       </c>
     </row>
     <row r="1961" spans="1:5" x14ac:dyDescent="0.25">
@@ -54586,7 +54586,7 @@
         <v>61</v>
       </c>
       <c r="E2102">
-        <v>96</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2103" spans="1:5" x14ac:dyDescent="0.25">
@@ -54603,7 +54603,7 @@
         <v>61</v>
       </c>
       <c r="E2103">
-        <v>93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2104" spans="1:5" x14ac:dyDescent="0.25">
@@ -59431,7 +59431,7 @@
         <v>88</v>
       </c>
       <c r="E2387">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2388" spans="1:5" x14ac:dyDescent="0.25">
@@ -62865,7 +62865,7 @@
         <v>88</v>
       </c>
       <c r="E2589">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2590" spans="1:5" x14ac:dyDescent="0.25">
@@ -67268,7 +67268,7 @@
         <v>61</v>
       </c>
       <c r="E2848">
-        <v>348</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2849" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -5096,7 +5096,7 @@
     <t>7453126326715</t>
   </si>
   <si>
-    <t>(pendiente de completar: 7453126326715)</t>
+    <t>BLUSA ML DAMA QUERIDA COLCOL</t>
   </si>
   <si>
     <t>7453126326722</t>
@@ -18512,7 +18512,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-09-01 a 2026-09-24)</t>
+    <t>Ventas (2026-09-01 a 2026-09-25)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -19609,7 +19609,7 @@
         <v>93</v>
       </c>
       <c r="E41">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -19660,7 +19660,7 @@
         <v>100</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -19677,7 +19677,7 @@
         <v>100</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -19694,7 +19694,7 @@
         <v>100</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -19711,7 +19711,7 @@
         <v>100</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -19728,7 +19728,7 @@
         <v>100</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -21751,7 +21751,7 @@
         <v>100</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -24420,7 +24420,7 @@
         <v>18</v>
       </c>
       <c r="E324">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -25253,7 +25253,7 @@
         <v>198</v>
       </c>
       <c r="E373">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -31390,7 +31390,7 @@
         <v>85</v>
       </c>
       <c r="E734">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -32002,7 +32002,7 @@
         <v>18</v>
       </c>
       <c r="E770">
-        <v>360</v>
+        <v>324</v>
       </c>
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.25">
@@ -32155,7 +32155,7 @@
         <v>13</v>
       </c>
       <c r="E779">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="780" spans="1:5" x14ac:dyDescent="0.25">
@@ -32716,7 +32716,7 @@
         <v>8</v>
       </c>
       <c r="E812">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.25">
@@ -33257,10 +33257,10 @@
         <v>1694</v>
       </c>
       <c r="D844" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E844">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.25">
@@ -33277,7 +33277,7 @@
         <v>13</v>
       </c>
       <c r="E845">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.25">
@@ -33294,7 +33294,7 @@
         <v>13</v>
       </c>
       <c r="E846">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.25">
@@ -33906,7 +33906,7 @@
         <v>8</v>
       </c>
       <c r="E882">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.25">
@@ -34773,7 +34773,7 @@
         <v>18</v>
       </c>
       <c r="E933">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="934" spans="1:5" x14ac:dyDescent="0.25">
@@ -34994,7 +34994,7 @@
         <v>41</v>
       </c>
       <c r="E946">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="947" spans="1:5" x14ac:dyDescent="0.25">
@@ -35062,7 +35062,7 @@
         <v>13</v>
       </c>
       <c r="E950">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="951" spans="1:5" x14ac:dyDescent="0.25">
@@ -35691,7 +35691,7 @@
         <v>8</v>
       </c>
       <c r="E987">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="988" spans="1:5" x14ac:dyDescent="0.25">
@@ -35708,7 +35708,7 @@
         <v>18</v>
       </c>
       <c r="E988">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.25">
@@ -36235,7 +36235,7 @@
         <v>198</v>
       </c>
       <c r="E1019">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="1020" spans="1:5" x14ac:dyDescent="0.25">
@@ -36252,7 +36252,7 @@
         <v>198</v>
       </c>
       <c r="E1020">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1021" spans="1:5" x14ac:dyDescent="0.25">
@@ -37476,7 +37476,7 @@
         <v>18</v>
       </c>
       <c r="E1092">
-        <v>148</v>
+        <v>248</v>
       </c>
     </row>
     <row r="1093" spans="1:5" x14ac:dyDescent="0.25">
@@ -37952,7 +37952,7 @@
         <v>198</v>
       </c>
       <c r="E1120">
-        <v>0</v>
+        <v>336</v>
       </c>
     </row>
     <row r="1121" spans="1:5" x14ac:dyDescent="0.25">
@@ -37986,7 +37986,7 @@
         <v>198</v>
       </c>
       <c r="E1122">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1123" spans="1:5" x14ac:dyDescent="0.25">
@@ -38003,7 +38003,7 @@
         <v>198</v>
       </c>
       <c r="E1123">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1124" spans="1:5" x14ac:dyDescent="0.25">
@@ -38020,7 +38020,7 @@
         <v>198</v>
       </c>
       <c r="E1124">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1125" spans="1:5" x14ac:dyDescent="0.25">
@@ -38717,7 +38717,7 @@
         <v>198</v>
       </c>
       <c r="E1165">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1166" spans="1:5" x14ac:dyDescent="0.25">
@@ -39465,7 +39465,7 @@
         <v>93</v>
       </c>
       <c r="E1209">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1210" spans="1:5" x14ac:dyDescent="0.25">
@@ -39618,7 +39618,7 @@
         <v>41</v>
       </c>
       <c r="E1218">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1219" spans="1:5" x14ac:dyDescent="0.25">
@@ -41573,7 +41573,7 @@
         <v>126</v>
       </c>
       <c r="E1333">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1334" spans="1:5" x14ac:dyDescent="0.25">
@@ -44582,7 +44582,7 @@
         <v>18</v>
       </c>
       <c r="E1510">
-        <v>29</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1511" spans="1:5" x14ac:dyDescent="0.25">
@@ -47200,7 +47200,7 @@
         <v>41</v>
       </c>
       <c r="E1664">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1665" spans="1:5" x14ac:dyDescent="0.25">
@@ -49410,7 +49410,7 @@
         <v>61</v>
       </c>
       <c r="E1794">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1795" spans="1:5" x14ac:dyDescent="0.25">
@@ -50617,7 +50617,7 @@
         <v>85</v>
       </c>
       <c r="E1865">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1866" spans="1:5" x14ac:dyDescent="0.25">
@@ -51331,7 +51331,7 @@
         <v>8</v>
       </c>
       <c r="E1907">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1908" spans="1:5" x14ac:dyDescent="0.25">
@@ -51552,7 +51552,7 @@
         <v>61</v>
       </c>
       <c r="E1920">
-        <v>81</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1921" spans="1:5" x14ac:dyDescent="0.25">
@@ -52385,7 +52385,7 @@
         <v>423</v>
       </c>
       <c r="E1969">
-        <v>355</v>
+        <v>915</v>
       </c>
     </row>
     <row r="1970" spans="1:5" x14ac:dyDescent="0.25">
@@ -54493,7 +54493,7 @@
         <v>61</v>
       </c>
       <c r="E2093">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2094" spans="1:5" x14ac:dyDescent="0.25">
@@ -54816,7 +54816,7 @@
         <v>61</v>
       </c>
       <c r="E2112">
-        <v>77</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2113" spans="1:5" x14ac:dyDescent="0.25">
@@ -59559,7 +59559,7 @@
         <v>8</v>
       </c>
       <c r="E2391">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2392" spans="1:5" x14ac:dyDescent="0.25">
@@ -62500,7 +62500,7 @@
         <v>8</v>
       </c>
       <c r="E2564">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2565" spans="1:5" x14ac:dyDescent="0.25">
@@ -62517,7 +62517,7 @@
         <v>8</v>
       </c>
       <c r="E2565">
-        <v>48</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2566" spans="1:5" x14ac:dyDescent="0.25">
@@ -63027,7 +63027,7 @@
         <v>8</v>
       </c>
       <c r="E2595">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2596" spans="1:5" x14ac:dyDescent="0.25">
@@ -65237,7 +65237,7 @@
         <v>8</v>
       </c>
       <c r="E2725">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2726" spans="1:5" x14ac:dyDescent="0.25">
@@ -67498,7 +67498,7 @@
         <v>61</v>
       </c>
       <c r="E2858">
-        <v>336</v>
+        <v>696</v>
       </c>
     </row>
     <row r="2859" spans="1:5" x14ac:dyDescent="0.25">
@@ -87682,10 +87682,10 @@
         <v>5</v>
       </c>
       <c r="B699" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="C699" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="D699" t="s">
         <v>13</v>
@@ -87705,10 +87705,10 @@
         <v>5</v>
       </c>
       <c r="B700" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="C700" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="D700" t="s">
         <v>13</v>
@@ -87728,10 +87728,10 @@
         <v>5</v>
       </c>
       <c r="B701" t="s">
-        <v>1697</v>
+        <v>1905</v>
       </c>
       <c r="C701" t="s">
-        <v>1698</v>
+        <v>1906</v>
       </c>
       <c r="D701" t="s">
         <v>13</v>
@@ -87751,10 +87751,10 @@
         <v>5</v>
       </c>
       <c r="B702" t="s">
-        <v>1905</v>
+        <v>2110</v>
       </c>
       <c r="C702" t="s">
-        <v>1906</v>
+        <v>2111</v>
       </c>
       <c r="D702" t="s">
         <v>13</v>
@@ -87774,10 +87774,10 @@
         <v>5</v>
       </c>
       <c r="B703" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="C703" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="D703" t="s">
         <v>13</v>
@@ -87797,10 +87797,10 @@
         <v>5</v>
       </c>
       <c r="B704" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="C704" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="D704" t="s">
         <v>13</v>
@@ -87820,10 +87820,10 @@
         <v>5</v>
       </c>
       <c r="B705" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="C705" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="D705" t="s">
         <v>13</v>
@@ -87843,10 +87843,10 @@
         <v>5</v>
       </c>
       <c r="B706" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="C706" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="D706" t="s">
         <v>13</v>
@@ -87866,10 +87866,10 @@
         <v>5</v>
       </c>
       <c r="B707" t="s">
-        <v>2118</v>
+        <v>80</v>
       </c>
       <c r="C707" t="s">
-        <v>2119</v>
+        <v>80</v>
       </c>
       <c r="D707" t="s">
         <v>13</v>
@@ -87881,7 +87881,7 @@
         <v>0</v>
       </c>
       <c r="H707" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.25">
@@ -87889,13 +87889,13 @@
         <v>5</v>
       </c>
       <c r="B708" t="s">
-        <v>80</v>
+        <v>5471</v>
       </c>
       <c r="C708" t="s">
-        <v>80</v>
+        <v>5472</v>
       </c>
       <c r="D708" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="E708">
         <v>0</v>
@@ -87912,13 +87912,13 @@
         <v>5</v>
       </c>
       <c r="B709" t="s">
-        <v>5471</v>
+        <v>1244</v>
       </c>
       <c r="C709" t="s">
-        <v>5472</v>
+        <v>1245</v>
       </c>
       <c r="D709" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="E709">
         <v>0</v>
@@ -87935,13 +87935,13 @@
         <v>5</v>
       </c>
       <c r="B710" t="s">
-        <v>1244</v>
+        <v>111</v>
       </c>
       <c r="C710" t="s">
-        <v>1245</v>
+        <v>112</v>
       </c>
       <c r="D710" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="E710">
         <v>0</v>
@@ -87958,13 +87958,13 @@
         <v>5</v>
       </c>
       <c r="B711" t="s">
-        <v>111</v>
+        <v>1105</v>
       </c>
       <c r="C711" t="s">
-        <v>112</v>
+        <v>1106</v>
       </c>
       <c r="D711" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="E711">
         <v>0</v>
@@ -87981,10 +87981,10 @@
         <v>5</v>
       </c>
       <c r="B712" t="s">
-        <v>1105</v>
+        <v>1757</v>
       </c>
       <c r="C712" t="s">
-        <v>1106</v>
+        <v>1758</v>
       </c>
       <c r="D712" t="s">
         <v>18</v>
@@ -88004,13 +88004,13 @@
         <v>5</v>
       </c>
       <c r="B713" t="s">
-        <v>1757</v>
+        <v>2377</v>
       </c>
       <c r="C713" t="s">
-        <v>1758</v>
+        <v>2378</v>
       </c>
       <c r="D713" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="E713">
         <v>0</v>
@@ -88019,7 +88019,7 @@
         <v>0</v>
       </c>
       <c r="H713" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.25">
@@ -88027,10 +88027,10 @@
         <v>5</v>
       </c>
       <c r="B714" t="s">
-        <v>2377</v>
+        <v>201</v>
       </c>
       <c r="C714" t="s">
-        <v>2378</v>
+        <v>202</v>
       </c>
       <c r="D714" t="s">
         <v>85</v>
@@ -88042,7 +88042,7 @@
         <v>0</v>
       </c>
       <c r="H714" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.25">
@@ -88050,13 +88050,13 @@
         <v>5</v>
       </c>
       <c r="B715" t="s">
-        <v>201</v>
+        <v>4808</v>
       </c>
       <c r="C715" t="s">
-        <v>202</v>
+        <v>4809</v>
       </c>
       <c r="D715" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E715">
         <v>0</v>
@@ -88073,13 +88073,13 @@
         <v>5</v>
       </c>
       <c r="B716" t="s">
-        <v>4808</v>
+        <v>811</v>
       </c>
       <c r="C716" t="s">
-        <v>4809</v>
+        <v>812</v>
       </c>
       <c r="D716" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="E716">
         <v>0</v>
@@ -88096,13 +88096,13 @@
         <v>5</v>
       </c>
       <c r="B717" t="s">
-        <v>811</v>
+        <v>143</v>
       </c>
       <c r="C717" t="s">
-        <v>812</v>
+        <v>144</v>
       </c>
       <c r="D717" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="E717">
         <v>0</v>
@@ -88119,13 +88119,13 @@
         <v>5</v>
       </c>
       <c r="B718" t="s">
-        <v>143</v>
+        <v>2142</v>
       </c>
       <c r="C718" t="s">
-        <v>144</v>
+        <v>2143</v>
       </c>
       <c r="D718" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="E718">
         <v>0</v>
@@ -88142,13 +88142,13 @@
         <v>5</v>
       </c>
       <c r="B719" t="s">
-        <v>2142</v>
+        <v>203</v>
       </c>
       <c r="C719" t="s">
-        <v>2143</v>
+        <v>204</v>
       </c>
       <c r="D719" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="E719">
         <v>0</v>
@@ -88165,13 +88165,13 @@
         <v>5</v>
       </c>
       <c r="B720" t="s">
-        <v>203</v>
+        <v>289</v>
       </c>
       <c r="C720" t="s">
-        <v>204</v>
+        <v>290</v>
       </c>
       <c r="D720" t="s">
-        <v>8</v>
+        <v>198</v>
       </c>
       <c r="E720">
         <v>0</v>
@@ -88188,10 +88188,10 @@
         <v>5</v>
       </c>
       <c r="B721" t="s">
-        <v>289</v>
+        <v>2442</v>
       </c>
       <c r="C721" t="s">
-        <v>290</v>
+        <v>2443</v>
       </c>
       <c r="D721" t="s">
         <v>198</v>
@@ -88211,10 +88211,10 @@
         <v>5</v>
       </c>
       <c r="B722" t="s">
-        <v>2442</v>
+        <v>2448</v>
       </c>
       <c r="C722" t="s">
-        <v>2443</v>
+        <v>2449</v>
       </c>
       <c r="D722" t="s">
         <v>198</v>
@@ -88234,10 +88234,10 @@
         <v>5</v>
       </c>
       <c r="B723" t="s">
-        <v>2448</v>
+        <v>2444</v>
       </c>
       <c r="C723" t="s">
-        <v>2449</v>
+        <v>2445</v>
       </c>
       <c r="D723" t="s">
         <v>198</v>
@@ -88257,10 +88257,10 @@
         <v>5</v>
       </c>
       <c r="B724" t="s">
-        <v>2444</v>
+        <v>2450</v>
       </c>
       <c r="C724" t="s">
-        <v>2445</v>
+        <v>2451</v>
       </c>
       <c r="D724" t="s">
         <v>198</v>
@@ -88280,10 +88280,10 @@
         <v>5</v>
       </c>
       <c r="B725" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="C725" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="D725" t="s">
         <v>198</v>
@@ -88303,10 +88303,10 @@
         <v>5</v>
       </c>
       <c r="B726" t="s">
-        <v>2452</v>
+        <v>2440</v>
       </c>
       <c r="C726" t="s">
-        <v>2453</v>
+        <v>2441</v>
       </c>
       <c r="D726" t="s">
         <v>198</v>
@@ -88326,13 +88326,13 @@
         <v>5</v>
       </c>
       <c r="B727" t="s">
-        <v>2440</v>
+        <v>2454</v>
       </c>
       <c r="C727" t="s">
-        <v>2441</v>
+        <v>2455</v>
       </c>
       <c r="D727" t="s">
-        <v>198</v>
+        <v>85</v>
       </c>
       <c r="E727">
         <v>0</v>
@@ -88349,10 +88349,10 @@
         <v>5</v>
       </c>
       <c r="B728" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="C728" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="D728" t="s">
         <v>85</v>
@@ -88372,13 +88372,13 @@
         <v>5</v>
       </c>
       <c r="B729" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="C729" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="D729" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="E729">
         <v>0</v>
@@ -88395,13 +88395,13 @@
         <v>5</v>
       </c>
       <c r="B730" t="s">
-        <v>2458</v>
+        <v>967</v>
       </c>
       <c r="C730" t="s">
-        <v>2459</v>
+        <v>968</v>
       </c>
       <c r="D730" t="s">
-        <v>198</v>
+        <v>85</v>
       </c>
       <c r="E730">
         <v>0</v>
@@ -88418,13 +88418,13 @@
         <v>5</v>
       </c>
       <c r="B731" t="s">
-        <v>967</v>
+        <v>2462</v>
       </c>
       <c r="C731" t="s">
-        <v>968</v>
+        <v>2463</v>
       </c>
       <c r="D731" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="E731">
         <v>0</v>
@@ -88441,13 +88441,13 @@
         <v>5</v>
       </c>
       <c r="B732" t="s">
-        <v>2462</v>
+        <v>2466</v>
       </c>
       <c r="C732" t="s">
-        <v>2463</v>
+        <v>2467</v>
       </c>
       <c r="D732" t="s">
-        <v>198</v>
+        <v>85</v>
       </c>
       <c r="E732">
         <v>0</v>
@@ -88464,10 +88464,10 @@
         <v>5</v>
       </c>
       <c r="B733" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="C733" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="D733" t="s">
         <v>85</v>
@@ -88487,13 +88487,13 @@
         <v>5</v>
       </c>
       <c r="B734" t="s">
-        <v>2464</v>
+        <v>1282</v>
       </c>
       <c r="C734" t="s">
-        <v>2465</v>
+        <v>1283</v>
       </c>
       <c r="D734" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E734">
         <v>0</v>
@@ -88510,13 +88510,13 @@
         <v>5</v>
       </c>
       <c r="B735" t="s">
-        <v>1282</v>
+        <v>1356</v>
       </c>
       <c r="C735" t="s">
-        <v>1283</v>
+        <v>1357</v>
       </c>
       <c r="D735" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E735">
         <v>0</v>
@@ -88533,10 +88533,10 @@
         <v>5</v>
       </c>
       <c r="B736" t="s">
-        <v>1356</v>
+        <v>1386</v>
       </c>
       <c r="C736" t="s">
-        <v>1357</v>
+        <v>1387</v>
       </c>
       <c r="D736" t="s">
         <v>85</v>
@@ -88556,10 +88556,10 @@
         <v>5</v>
       </c>
       <c r="B737" t="s">
-        <v>1386</v>
+        <v>1430</v>
       </c>
       <c r="C737" t="s">
-        <v>1387</v>
+        <v>1431</v>
       </c>
       <c r="D737" t="s">
         <v>85</v>
@@ -88579,10 +88579,10 @@
         <v>5</v>
       </c>
       <c r="B738" t="s">
-        <v>1430</v>
+        <v>1354</v>
       </c>
       <c r="C738" t="s">
-        <v>1431</v>
+        <v>1355</v>
       </c>
       <c r="D738" t="s">
         <v>85</v>
@@ -88602,10 +88602,10 @@
         <v>5</v>
       </c>
       <c r="B739" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C739" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D739" t="s">
         <v>85</v>
@@ -88625,10 +88625,10 @@
         <v>5</v>
       </c>
       <c r="B740" t="s">
-        <v>1352</v>
+        <v>685</v>
       </c>
       <c r="C740" t="s">
-        <v>1353</v>
+        <v>686</v>
       </c>
       <c r="D740" t="s">
         <v>85</v>
@@ -88648,13 +88648,13 @@
         <v>5</v>
       </c>
       <c r="B741" t="s">
-        <v>685</v>
+        <v>1570</v>
       </c>
       <c r="C741" t="s">
-        <v>686</v>
+        <v>1571</v>
       </c>
       <c r="D741" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E741">
         <v>0</v>
@@ -88663,7 +88663,7 @@
         <v>0</v>
       </c>
       <c r="H741" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
@@ -88671,13 +88671,13 @@
         <v>5</v>
       </c>
       <c r="B742" t="s">
-        <v>1570</v>
+        <v>2468</v>
       </c>
       <c r="C742" t="s">
-        <v>1571</v>
+        <v>2469</v>
       </c>
       <c r="D742" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E742">
         <v>0</v>
@@ -88686,7 +88686,7 @@
         <v>0</v>
       </c>
       <c r="H742" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
@@ -88694,10 +88694,10 @@
         <v>5</v>
       </c>
       <c r="B743" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="C743" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D743" t="s">
         <v>85</v>
@@ -88717,10 +88717,10 @@
         <v>5</v>
       </c>
       <c r="B744" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="C744" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="D744" t="s">
         <v>85</v>
@@ -88740,10 +88740,10 @@
         <v>5</v>
       </c>
       <c r="B745" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="C745" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="D745" t="s">
         <v>85</v>
@@ -88763,10 +88763,10 @@
         <v>5</v>
       </c>
       <c r="B746" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="C746" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="D746" t="s">
         <v>85</v>
@@ -88786,10 +88786,10 @@
         <v>5</v>
       </c>
       <c r="B747" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="C747" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="D747" t="s">
         <v>85</v>
@@ -88809,10 +88809,10 @@
         <v>5</v>
       </c>
       <c r="B748" t="s">
-        <v>2478</v>
+        <v>2460</v>
       </c>
       <c r="C748" t="s">
-        <v>2479</v>
+        <v>2461</v>
       </c>
       <c r="D748" t="s">
         <v>85</v>
@@ -88832,10 +88832,10 @@
         <v>5</v>
       </c>
       <c r="B749" t="s">
-        <v>2460</v>
+        <v>2480</v>
       </c>
       <c r="C749" t="s">
-        <v>2461</v>
+        <v>2481</v>
       </c>
       <c r="D749" t="s">
         <v>85</v>
@@ -88855,10 +88855,10 @@
         <v>5</v>
       </c>
       <c r="B750" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
       <c r="C750" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="D750" t="s">
         <v>85</v>
@@ -88878,10 +88878,10 @@
         <v>5</v>
       </c>
       <c r="B751" t="s">
-        <v>2484</v>
+        <v>1449</v>
       </c>
       <c r="C751" t="s">
-        <v>2485</v>
+        <v>1450</v>
       </c>
       <c r="D751" t="s">
         <v>85</v>
@@ -88901,10 +88901,10 @@
         <v>5</v>
       </c>
       <c r="B752" t="s">
-        <v>1449</v>
+        <v>2490</v>
       </c>
       <c r="C752" t="s">
-        <v>1450</v>
+        <v>2491</v>
       </c>
       <c r="D752" t="s">
         <v>85</v>
@@ -88924,10 +88924,10 @@
         <v>5</v>
       </c>
       <c r="B753" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="C753" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="D753" t="s">
         <v>85</v>
@@ -88947,10 +88947,10 @@
         <v>5</v>
       </c>
       <c r="B754" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="C754" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="D754" t="s">
         <v>85</v>
@@ -88970,10 +88970,10 @@
         <v>5</v>
       </c>
       <c r="B755" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="C755" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="D755" t="s">
         <v>85</v>
@@ -88993,10 +88993,10 @@
         <v>5</v>
       </c>
       <c r="B756" t="s">
-        <v>2496</v>
+        <v>2500</v>
       </c>
       <c r="C756" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
       <c r="D756" t="s">
         <v>85</v>
@@ -89016,10 +89016,10 @@
         <v>5</v>
       </c>
       <c r="B757" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="C757" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="D757" t="s">
         <v>85</v>
@@ -89039,10 +89039,10 @@
         <v>5</v>
       </c>
       <c r="B758" t="s">
-        <v>2498</v>
+        <v>1477</v>
       </c>
       <c r="C758" t="s">
-        <v>2499</v>
+        <v>1478</v>
       </c>
       <c r="D758" t="s">
         <v>85</v>
@@ -89062,10 +89062,10 @@
         <v>5</v>
       </c>
       <c r="B759" t="s">
-        <v>1477</v>
+        <v>2563</v>
       </c>
       <c r="C759" t="s">
-        <v>1478</v>
+        <v>2564</v>
       </c>
       <c r="D759" t="s">
         <v>85</v>
@@ -89085,13 +89085,13 @@
         <v>5</v>
       </c>
       <c r="B760" t="s">
-        <v>2563</v>
+        <v>2486</v>
       </c>
       <c r="C760" t="s">
-        <v>2564</v>
+        <v>2487</v>
       </c>
       <c r="D760" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="E760">
         <v>0</v>
@@ -89108,13 +89108,13 @@
         <v>5</v>
       </c>
       <c r="B761" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="C761" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="D761" t="s">
-        <v>126</v>
+        <v>198</v>
       </c>
       <c r="E761">
         <v>0</v>
@@ -89131,10 +89131,10 @@
         <v>5</v>
       </c>
       <c r="B762" t="s">
-        <v>2488</v>
+        <v>2482</v>
       </c>
       <c r="C762" t="s">
-        <v>2489</v>
+        <v>2483</v>
       </c>
       <c r="D762" t="s">
         <v>198</v>
@@ -89154,13 +89154,13 @@
         <v>5</v>
       </c>
       <c r="B763" t="s">
-        <v>2482</v>
+        <v>2502</v>
       </c>
       <c r="C763" t="s">
-        <v>2483</v>
+        <v>2503</v>
       </c>
       <c r="D763" t="s">
-        <v>198</v>
+        <v>48</v>
       </c>
       <c r="E763">
         <v>0</v>
@@ -89177,10 +89177,10 @@
         <v>5</v>
       </c>
       <c r="B764" t="s">
-        <v>2502</v>
+        <v>6064</v>
       </c>
       <c r="C764" t="s">
-        <v>2503</v>
+        <v>6065</v>
       </c>
       <c r="D764" t="s">
         <v>48</v>
@@ -89200,10 +89200,10 @@
         <v>5</v>
       </c>
       <c r="B765" t="s">
-        <v>6064</v>
+        <v>2504</v>
       </c>
       <c r="C765" t="s">
-        <v>6065</v>
+        <v>2505</v>
       </c>
       <c r="D765" t="s">
         <v>48</v>
@@ -89223,13 +89223,13 @@
         <v>5</v>
       </c>
       <c r="B766" t="s">
-        <v>2504</v>
+        <v>2512</v>
       </c>
       <c r="C766" t="s">
-        <v>2505</v>
+        <v>2513</v>
       </c>
       <c r="D766" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="E766">
         <v>0</v>
@@ -89246,13 +89246,13 @@
         <v>5</v>
       </c>
       <c r="B767" t="s">
-        <v>2512</v>
+        <v>2549</v>
       </c>
       <c r="C767" t="s">
-        <v>2513</v>
+        <v>2550</v>
       </c>
       <c r="D767" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="E767">
         <v>0</v>
@@ -89269,13 +89269,13 @@
         <v>5</v>
       </c>
       <c r="B768" t="s">
-        <v>2549</v>
+        <v>127</v>
       </c>
       <c r="C768" t="s">
-        <v>2550</v>
+        <v>128</v>
       </c>
       <c r="D768" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="E768">
         <v>0</v>
@@ -89292,10 +89292,10 @@
         <v>5</v>
       </c>
       <c r="B769" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C769" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D769" t="s">
         <v>41</v>
@@ -89315,10 +89315,10 @@
         <v>5</v>
       </c>
       <c r="B770" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C770" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D770" t="s">
         <v>41</v>
@@ -89338,13 +89338,13 @@
         <v>5</v>
       </c>
       <c r="B771" t="s">
-        <v>131</v>
+        <v>2124</v>
       </c>
       <c r="C771" t="s">
-        <v>132</v>
+        <v>2125</v>
       </c>
       <c r="D771" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="E771">
         <v>0</v>
@@ -89361,10 +89361,10 @@
         <v>5</v>
       </c>
       <c r="B772" t="s">
-        <v>2124</v>
+        <v>454</v>
       </c>
       <c r="C772" t="s">
-        <v>2125</v>
+        <v>455</v>
       </c>
       <c r="D772" t="s">
         <v>88</v>
@@ -89384,13 +89384,13 @@
         <v>5</v>
       </c>
       <c r="B773" t="s">
-        <v>454</v>
+        <v>2561</v>
       </c>
       <c r="C773" t="s">
-        <v>455</v>
+        <v>2562</v>
       </c>
       <c r="D773" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E773">
         <v>0</v>
@@ -89407,10 +89407,10 @@
         <v>5</v>
       </c>
       <c r="B774" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="C774" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="D774" t="s">
         <v>85</v>
@@ -89430,10 +89430,10 @@
         <v>5</v>
       </c>
       <c r="B775" t="s">
-        <v>2559</v>
+        <v>2565</v>
       </c>
       <c r="C775" t="s">
-        <v>2560</v>
+        <v>2566</v>
       </c>
       <c r="D775" t="s">
         <v>85</v>
@@ -89453,10 +89453,10 @@
         <v>5</v>
       </c>
       <c r="B776" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="C776" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
       <c r="D776" t="s">
         <v>85</v>
@@ -89476,10 +89476,10 @@
         <v>5</v>
       </c>
       <c r="B777" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="C777" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="D777" t="s">
         <v>85</v>
@@ -89499,10 +89499,10 @@
         <v>5</v>
       </c>
       <c r="B778" t="s">
-        <v>2567</v>
+        <v>2506</v>
       </c>
       <c r="C778" t="s">
-        <v>2568</v>
+        <v>2507</v>
       </c>
       <c r="D778" t="s">
         <v>85</v>
@@ -89522,10 +89522,10 @@
         <v>5</v>
       </c>
       <c r="B779" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="C779" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="D779" t="s">
         <v>85</v>
@@ -89545,10 +89545,10 @@
         <v>5</v>
       </c>
       <c r="B780" t="s">
-        <v>2508</v>
+        <v>2571</v>
       </c>
       <c r="C780" t="s">
-        <v>2509</v>
+        <v>2572</v>
       </c>
       <c r="D780" t="s">
         <v>85</v>
@@ -89568,10 +89568,10 @@
         <v>5</v>
       </c>
       <c r="B781" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="C781" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="D781" t="s">
         <v>85</v>
@@ -89591,10 +89591,10 @@
         <v>5</v>
       </c>
       <c r="B782" t="s">
-        <v>2573</v>
+        <v>2547</v>
       </c>
       <c r="C782" t="s">
-        <v>2574</v>
+        <v>2548</v>
       </c>
       <c r="D782" t="s">
         <v>85</v>
@@ -89614,10 +89614,10 @@
         <v>5</v>
       </c>
       <c r="B783" t="s">
-        <v>2547</v>
+        <v>2575</v>
       </c>
       <c r="C783" t="s">
-        <v>2548</v>
+        <v>2576</v>
       </c>
       <c r="D783" t="s">
         <v>85</v>
@@ -89637,13 +89637,13 @@
         <v>5</v>
       </c>
       <c r="B784" t="s">
-        <v>2575</v>
+        <v>2581</v>
       </c>
       <c r="C784" t="s">
-        <v>2576</v>
+        <v>2582</v>
       </c>
       <c r="D784" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="E784">
         <v>0</v>
@@ -89660,13 +89660,13 @@
         <v>5</v>
       </c>
       <c r="B785" t="s">
-        <v>2581</v>
+        <v>135</v>
       </c>
       <c r="C785" t="s">
-        <v>2582</v>
+        <v>136</v>
       </c>
       <c r="D785" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E785">
         <v>0</v>
@@ -89683,13 +89683,13 @@
         <v>5</v>
       </c>
       <c r="B786" t="s">
-        <v>135</v>
+        <v>2583</v>
       </c>
       <c r="C786" t="s">
-        <v>136</v>
+        <v>2584</v>
       </c>
       <c r="D786" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="E786">
         <v>0</v>
@@ -89706,13 +89706,13 @@
         <v>5</v>
       </c>
       <c r="B787" t="s">
-        <v>2583</v>
+        <v>2229</v>
       </c>
       <c r="C787" t="s">
-        <v>2584</v>
+        <v>2230</v>
       </c>
       <c r="D787" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E787">
         <v>0</v>
@@ -89729,10 +89729,10 @@
         <v>5</v>
       </c>
       <c r="B788" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="C788" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="D788" t="s">
         <v>41</v>
@@ -89752,13 +89752,13 @@
         <v>5</v>
       </c>
       <c r="B789" t="s">
-        <v>2231</v>
+        <v>2649</v>
       </c>
       <c r="C789" t="s">
-        <v>2232</v>
+        <v>2650</v>
       </c>
       <c r="D789" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="E789">
         <v>0</v>
@@ -89775,13 +89775,13 @@
         <v>5</v>
       </c>
       <c r="B790" t="s">
-        <v>2649</v>
+        <v>2589</v>
       </c>
       <c r="C790" t="s">
-        <v>2650</v>
+        <v>2590</v>
       </c>
       <c r="D790" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="E790">
         <v>0</v>
@@ -89798,13 +89798,13 @@
         <v>5</v>
       </c>
       <c r="B791" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="C791" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="D791" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="E791">
         <v>0</v>
@@ -89821,10 +89821,10 @@
         <v>5</v>
       </c>
       <c r="B792" t="s">
-        <v>2591</v>
+        <v>2599</v>
       </c>
       <c r="C792" t="s">
-        <v>2592</v>
+        <v>2600</v>
       </c>
       <c r="D792" t="s">
         <v>8</v>
@@ -89844,13 +89844,13 @@
         <v>5</v>
       </c>
       <c r="B793" t="s">
-        <v>2599</v>
+        <v>2579</v>
       </c>
       <c r="C793" t="s">
-        <v>2600</v>
+        <v>2580</v>
       </c>
       <c r="D793" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E793">
         <v>0</v>
@@ -89867,13 +89867,13 @@
         <v>5</v>
       </c>
       <c r="B794" t="s">
-        <v>2579</v>
+        <v>2593</v>
       </c>
       <c r="C794" t="s">
-        <v>2580</v>
+        <v>2594</v>
       </c>
       <c r="D794" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E794">
         <v>0</v>
@@ -89890,10 +89890,10 @@
         <v>5</v>
       </c>
       <c r="B795" t="s">
-        <v>2593</v>
+        <v>4043</v>
       </c>
       <c r="C795" t="s">
-        <v>2594</v>
+        <v>4044</v>
       </c>
       <c r="D795" t="s">
         <v>8</v>
@@ -89913,10 +89913,10 @@
         <v>5</v>
       </c>
       <c r="B796" t="s">
-        <v>4043</v>
+        <v>2603</v>
       </c>
       <c r="C796" t="s">
-        <v>4044</v>
+        <v>2604</v>
       </c>
       <c r="D796" t="s">
         <v>8</v>
@@ -89936,13 +89936,13 @@
         <v>5</v>
       </c>
       <c r="B797" t="s">
-        <v>2603</v>
+        <v>1404</v>
       </c>
       <c r="C797" t="s">
-        <v>2604</v>
+        <v>1405</v>
       </c>
       <c r="D797" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E797">
         <v>0</v>
@@ -89959,13 +89959,13 @@
         <v>5</v>
       </c>
       <c r="B798" t="s">
-        <v>1404</v>
+        <v>2653</v>
       </c>
       <c r="C798" t="s">
-        <v>1405</v>
+        <v>2654</v>
       </c>
       <c r="D798" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E798">
         <v>0</v>
@@ -89982,10 +89982,10 @@
         <v>5</v>
       </c>
       <c r="B799" t="s">
-        <v>2653</v>
+        <v>2595</v>
       </c>
       <c r="C799" t="s">
-        <v>2654</v>
+        <v>2596</v>
       </c>
       <c r="D799" t="s">
         <v>8</v>
@@ -90005,10 +90005,10 @@
         <v>5</v>
       </c>
       <c r="B800" t="s">
-        <v>2595</v>
+        <v>2949</v>
       </c>
       <c r="C800" t="s">
-        <v>2596</v>
+        <v>2950</v>
       </c>
       <c r="D800" t="s">
         <v>8</v>
@@ -90028,10 +90028,10 @@
         <v>5</v>
       </c>
       <c r="B801" t="s">
-        <v>2949</v>
+        <v>2607</v>
       </c>
       <c r="C801" t="s">
-        <v>2950</v>
+        <v>2608</v>
       </c>
       <c r="D801" t="s">
         <v>8</v>
@@ -90051,13 +90051,13 @@
         <v>5</v>
       </c>
       <c r="B802" t="s">
-        <v>2607</v>
+        <v>1406</v>
       </c>
       <c r="C802" t="s">
-        <v>2608</v>
+        <v>1407</v>
       </c>
       <c r="D802" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E802">
         <v>0</v>
@@ -90097,13 +90097,13 @@
         <v>5</v>
       </c>
       <c r="B804" t="s">
-        <v>1406</v>
+        <v>2609</v>
       </c>
       <c r="C804" t="s">
-        <v>1407</v>
+        <v>2610</v>
       </c>
       <c r="D804" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="E804">
         <v>0</v>
@@ -90120,10 +90120,10 @@
         <v>5</v>
       </c>
       <c r="B805" t="s">
-        <v>2609</v>
+        <v>2585</v>
       </c>
       <c r="C805" t="s">
-        <v>2610</v>
+        <v>2586</v>
       </c>
       <c r="D805" t="s">
         <v>88</v>
@@ -90143,10 +90143,10 @@
         <v>5</v>
       </c>
       <c r="B806" t="s">
-        <v>2585</v>
+        <v>2605</v>
       </c>
       <c r="C806" t="s">
-        <v>2586</v>
+        <v>2606</v>
       </c>
       <c r="D806" t="s">
         <v>88</v>
@@ -90166,13 +90166,13 @@
         <v>5</v>
       </c>
       <c r="B807" t="s">
-        <v>2605</v>
+        <v>2769</v>
       </c>
       <c r="C807" t="s">
-        <v>2606</v>
+        <v>2770</v>
       </c>
       <c r="D807" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="E807">
         <v>0</v>
@@ -90189,10 +90189,10 @@
         <v>5</v>
       </c>
       <c r="B808" t="s">
-        <v>2769</v>
+        <v>2611</v>
       </c>
       <c r="C808" t="s">
-        <v>2770</v>
+        <v>2612</v>
       </c>
       <c r="D808" t="s">
         <v>41</v>
@@ -90212,13 +90212,13 @@
         <v>5</v>
       </c>
       <c r="B809" t="s">
-        <v>2611</v>
+        <v>2613</v>
       </c>
       <c r="C809" t="s">
-        <v>2612</v>
+        <v>2614</v>
       </c>
       <c r="D809" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E809">
         <v>0</v>
@@ -90235,10 +90235,10 @@
         <v>5</v>
       </c>
       <c r="B810" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="C810" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
       <c r="D810" t="s">
         <v>8</v>
@@ -90258,10 +90258,10 @@
         <v>5</v>
       </c>
       <c r="B811" t="s">
-        <v>2615</v>
+        <v>2597</v>
       </c>
       <c r="C811" t="s">
-        <v>2616</v>
+        <v>2598</v>
       </c>
       <c r="D811" t="s">
         <v>8</v>
@@ -90281,10 +90281,10 @@
         <v>5</v>
       </c>
       <c r="B812" t="s">
-        <v>2597</v>
+        <v>2619</v>
       </c>
       <c r="C812" t="s">
-        <v>2598</v>
+        <v>2620</v>
       </c>
       <c r="D812" t="s">
         <v>8</v>
@@ -90304,10 +90304,10 @@
         <v>5</v>
       </c>
       <c r="B813" t="s">
-        <v>2619</v>
+        <v>2621</v>
       </c>
       <c r="C813" t="s">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="D813" t="s">
         <v>8</v>
@@ -90327,10 +90327,10 @@
         <v>5</v>
       </c>
       <c r="B814" t="s">
-        <v>2621</v>
+        <v>2601</v>
       </c>
       <c r="C814" t="s">
-        <v>2622</v>
+        <v>2602</v>
       </c>
       <c r="D814" t="s">
         <v>8</v>
@@ -90350,10 +90350,10 @@
         <v>5</v>
       </c>
       <c r="B815" t="s">
-        <v>2601</v>
+        <v>2053</v>
       </c>
       <c r="C815" t="s">
-        <v>2602</v>
+        <v>2054</v>
       </c>
       <c r="D815" t="s">
         <v>8</v>
@@ -90373,13 +90373,13 @@
         <v>5</v>
       </c>
       <c r="B816" t="s">
-        <v>2053</v>
+        <v>2146</v>
       </c>
       <c r="C816" t="s">
-        <v>2054</v>
+        <v>2147</v>
       </c>
       <c r="D816" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="E816">
         <v>0</v>
@@ -90396,13 +90396,13 @@
         <v>5</v>
       </c>
       <c r="B817" t="s">
-        <v>2146</v>
+        <v>1851</v>
       </c>
       <c r="C817" t="s">
-        <v>2147</v>
+        <v>1852</v>
       </c>
       <c r="D817" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E817">
         <v>0</v>
@@ -90419,10 +90419,10 @@
         <v>5</v>
       </c>
       <c r="B818" t="s">
-        <v>1851</v>
+        <v>2669</v>
       </c>
       <c r="C818" t="s">
-        <v>1852</v>
+        <v>2670</v>
       </c>
       <c r="D818" t="s">
         <v>61</v>
@@ -90442,10 +90442,10 @@
         <v>5</v>
       </c>
       <c r="B819" t="s">
-        <v>2669</v>
+        <v>2683</v>
       </c>
       <c r="C819" t="s">
-        <v>2670</v>
+        <v>2684</v>
       </c>
       <c r="D819" t="s">
         <v>61</v>
@@ -90465,10 +90465,10 @@
         <v>5</v>
       </c>
       <c r="B820" t="s">
-        <v>2683</v>
+        <v>1554</v>
       </c>
       <c r="C820" t="s">
-        <v>2684</v>
+        <v>1555</v>
       </c>
       <c r="D820" t="s">
         <v>61</v>
@@ -90488,10 +90488,10 @@
         <v>5</v>
       </c>
       <c r="B821" t="s">
-        <v>1554</v>
+        <v>2673</v>
       </c>
       <c r="C821" t="s">
-        <v>1555</v>
+        <v>2674</v>
       </c>
       <c r="D821" t="s">
         <v>61</v>
@@ -90511,10 +90511,10 @@
         <v>5</v>
       </c>
       <c r="B822" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="C822" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="D822" t="s">
         <v>61</v>
@@ -90534,10 +90534,10 @@
         <v>5</v>
       </c>
       <c r="B823" t="s">
-        <v>2671</v>
+        <v>2677</v>
       </c>
       <c r="C823" t="s">
-        <v>2672</v>
+        <v>2678</v>
       </c>
       <c r="D823" t="s">
         <v>61</v>
@@ -90557,13 +90557,13 @@
         <v>5</v>
       </c>
       <c r="B824" t="s">
-        <v>2677</v>
+        <v>837</v>
       </c>
       <c r="C824" t="s">
-        <v>2678</v>
+        <v>838</v>
       </c>
       <c r="D824" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E824">
         <v>0</v>
@@ -90580,13 +90580,13 @@
         <v>5</v>
       </c>
       <c r="B825" t="s">
-        <v>837</v>
+        <v>245</v>
       </c>
       <c r="C825" t="s">
-        <v>838</v>
+        <v>246</v>
       </c>
       <c r="D825" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E825">
         <v>0</v>
@@ -90603,10 +90603,10 @@
         <v>5</v>
       </c>
       <c r="B826" t="s">
-        <v>245</v>
+        <v>2705</v>
       </c>
       <c r="C826" t="s">
-        <v>246</v>
+        <v>2706</v>
       </c>
       <c r="D826" t="s">
         <v>61</v>
@@ -90626,13 +90626,13 @@
         <v>5</v>
       </c>
       <c r="B827" t="s">
-        <v>2705</v>
+        <v>2679</v>
       </c>
       <c r="C827" t="s">
-        <v>2706</v>
+        <v>2680</v>
       </c>
       <c r="D827" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E827">
         <v>0</v>
@@ -90649,10 +90649,10 @@
         <v>5</v>
       </c>
       <c r="B828" t="s">
-        <v>2679</v>
+        <v>2707</v>
       </c>
       <c r="C828" t="s">
-        <v>2680</v>
+        <v>2708</v>
       </c>
       <c r="D828" t="s">
         <v>41</v>
@@ -90672,13 +90672,13 @@
         <v>5</v>
       </c>
       <c r="B829" t="s">
-        <v>2707</v>
+        <v>2691</v>
       </c>
       <c r="C829" t="s">
-        <v>2708</v>
+        <v>2692</v>
       </c>
       <c r="D829" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E829">
         <v>0</v>
@@ -90695,13 +90695,13 @@
         <v>5</v>
       </c>
       <c r="B830" t="s">
-        <v>2691</v>
+        <v>1743</v>
       </c>
       <c r="C830" t="s">
-        <v>2692</v>
+        <v>1744</v>
       </c>
       <c r="D830" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E830">
         <v>0</v>
@@ -90718,10 +90718,10 @@
         <v>5</v>
       </c>
       <c r="B831" t="s">
-        <v>1743</v>
+        <v>2681</v>
       </c>
       <c r="C831" t="s">
-        <v>1744</v>
+        <v>2682</v>
       </c>
       <c r="D831" t="s">
         <v>41</v>
@@ -90741,13 +90741,13 @@
         <v>5</v>
       </c>
       <c r="B832" t="s">
-        <v>2681</v>
+        <v>2687</v>
       </c>
       <c r="C832" t="s">
-        <v>2682</v>
+        <v>2688</v>
       </c>
       <c r="D832" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E832">
         <v>0</v>
@@ -90764,10 +90764,10 @@
         <v>5</v>
       </c>
       <c r="B833" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="C833" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="D833" t="s">
         <v>61</v>
@@ -90787,10 +90787,10 @@
         <v>5</v>
       </c>
       <c r="B834" t="s">
-        <v>2685</v>
+        <v>2761</v>
       </c>
       <c r="C834" t="s">
-        <v>2686</v>
+        <v>2762</v>
       </c>
       <c r="D834" t="s">
         <v>61</v>
@@ -90810,13 +90810,13 @@
         <v>5</v>
       </c>
       <c r="B835" t="s">
-        <v>2761</v>
+        <v>2763</v>
       </c>
       <c r="C835" t="s">
-        <v>2762</v>
+        <v>2764</v>
       </c>
       <c r="D835" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E835">
         <v>0</v>
@@ -90833,13 +90833,13 @@
         <v>5</v>
       </c>
       <c r="B836" t="s">
-        <v>2763</v>
+        <v>2767</v>
       </c>
       <c r="C836" t="s">
-        <v>2764</v>
+        <v>2768</v>
       </c>
       <c r="D836" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E836">
         <v>0</v>
@@ -90856,10 +90856,10 @@
         <v>5</v>
       </c>
       <c r="B837" t="s">
-        <v>2767</v>
+        <v>2689</v>
       </c>
       <c r="C837" t="s">
-        <v>2768</v>
+        <v>2690</v>
       </c>
       <c r="D837" t="s">
         <v>61</v>
@@ -90879,10 +90879,10 @@
         <v>5</v>
       </c>
       <c r="B838" t="s">
-        <v>2689</v>
+        <v>188</v>
       </c>
       <c r="C838" t="s">
-        <v>2690</v>
+        <v>189</v>
       </c>
       <c r="D838" t="s">
         <v>61</v>
@@ -90902,13 +90902,13 @@
         <v>5</v>
       </c>
       <c r="B839" t="s">
-        <v>188</v>
+        <v>5617</v>
       </c>
       <c r="C839" t="s">
-        <v>189</v>
+        <v>5618</v>
       </c>
       <c r="D839" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E839">
         <v>0</v>
@@ -90925,13 +90925,13 @@
         <v>5</v>
       </c>
       <c r="B840" t="s">
-        <v>5617</v>
+        <v>2737</v>
       </c>
       <c r="C840" t="s">
-        <v>5618</v>
+        <v>2738</v>
       </c>
       <c r="D840" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="E840">
         <v>0</v>
@@ -90948,13 +90948,13 @@
         <v>5</v>
       </c>
       <c r="B841" t="s">
-        <v>2737</v>
+        <v>809</v>
       </c>
       <c r="C841" t="s">
-        <v>2738</v>
+        <v>810</v>
       </c>
       <c r="D841" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E841">
         <v>0</v>
@@ -90971,13 +90971,13 @@
         <v>5</v>
       </c>
       <c r="B842" t="s">
-        <v>809</v>
+        <v>2709</v>
       </c>
       <c r="C842" t="s">
-        <v>810</v>
+        <v>2710</v>
       </c>
       <c r="D842" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E842">
         <v>0</v>
@@ -90994,10 +90994,10 @@
         <v>5</v>
       </c>
       <c r="B843" t="s">
-        <v>2709</v>
+        <v>184</v>
       </c>
       <c r="C843" t="s">
-        <v>2710</v>
+        <v>185</v>
       </c>
       <c r="D843" t="s">
         <v>8</v>
@@ -91017,10 +91017,10 @@
         <v>5</v>
       </c>
       <c r="B844" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C844" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D844" t="s">
         <v>8</v>
@@ -91032,7 +91032,7 @@
         <v>0</v>
       </c>
       <c r="H844" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="845" spans="1:8" x14ac:dyDescent="0.25">
@@ -91040,10 +91040,10 @@
         <v>5</v>
       </c>
       <c r="B845" t="s">
-        <v>186</v>
+        <v>2713</v>
       </c>
       <c r="C845" t="s">
-        <v>187</v>
+        <v>2714</v>
       </c>
       <c r="D845" t="s">
         <v>8</v>
@@ -91063,10 +91063,10 @@
         <v>5</v>
       </c>
       <c r="B846" t="s">
-        <v>2713</v>
+        <v>2719</v>
       </c>
       <c r="C846" t="s">
-        <v>2714</v>
+        <v>2720</v>
       </c>
       <c r="D846" t="s">
         <v>8</v>
@@ -91078,7 +91078,7 @@
         <v>0</v>
       </c>
       <c r="H846" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
@@ -91086,10 +91086,10 @@
         <v>5</v>
       </c>
       <c r="B847" t="s">
-        <v>2719</v>
+        <v>2715</v>
       </c>
       <c r="C847" t="s">
-        <v>2720</v>
+        <v>2716</v>
       </c>
       <c r="D847" t="s">
         <v>8</v>
@@ -91109,10 +91109,10 @@
         <v>5</v>
       </c>
       <c r="B848" t="s">
-        <v>2715</v>
+        <v>1797</v>
       </c>
       <c r="C848" t="s">
-        <v>2716</v>
+        <v>1798</v>
       </c>
       <c r="D848" t="s">
         <v>8</v>
@@ -91132,10 +91132,10 @@
         <v>5</v>
       </c>
       <c r="B849" t="s">
-        <v>1797</v>
+        <v>2747</v>
       </c>
       <c r="C849" t="s">
-        <v>1798</v>
+        <v>2748</v>
       </c>
       <c r="D849" t="s">
         <v>8</v>
@@ -91155,10 +91155,10 @@
         <v>5</v>
       </c>
       <c r="B850" t="s">
-        <v>2747</v>
+        <v>2723</v>
       </c>
       <c r="C850" t="s">
-        <v>2748</v>
+        <v>2724</v>
       </c>
       <c r="D850" t="s">
         <v>8</v>
@@ -91170,7 +91170,7 @@
         <v>0</v>
       </c>
       <c r="H850" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
@@ -91178,10 +91178,10 @@
         <v>5</v>
       </c>
       <c r="B851" t="s">
-        <v>2723</v>
+        <v>2753</v>
       </c>
       <c r="C851" t="s">
-        <v>2724</v>
+        <v>2754</v>
       </c>
       <c r="D851" t="s">
         <v>8</v>
@@ -91193,7 +91193,7 @@
         <v>0</v>
       </c>
       <c r="H851" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
@@ -91201,10 +91201,10 @@
         <v>5</v>
       </c>
       <c r="B852" t="s">
-        <v>2753</v>
+        <v>257</v>
       </c>
       <c r="C852" t="s">
-        <v>2754</v>
+        <v>258</v>
       </c>
       <c r="D852" t="s">
         <v>8</v>
@@ -91216,7 +91216,7 @@
         <v>0</v>
       </c>
       <c r="H852" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
@@ -91224,10 +91224,10 @@
         <v>5</v>
       </c>
       <c r="B853" t="s">
-        <v>257</v>
+        <v>1829</v>
       </c>
       <c r="C853" t="s">
-        <v>258</v>
+        <v>1830</v>
       </c>
       <c r="D853" t="s">
         <v>8</v>
@@ -91239,7 +91239,7 @@
         <v>0</v>
       </c>
       <c r="H853" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
@@ -91247,10 +91247,10 @@
         <v>5</v>
       </c>
       <c r="B854" t="s">
-        <v>1829</v>
+        <v>255</v>
       </c>
       <c r="C854" t="s">
-        <v>1830</v>
+        <v>256</v>
       </c>
       <c r="D854" t="s">
         <v>8</v>
@@ -91262,7 +91262,7 @@
         <v>0</v>
       </c>
       <c r="H854" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
@@ -91270,10 +91270,10 @@
         <v>5</v>
       </c>
       <c r="B855" t="s">
-        <v>255</v>
+        <v>1228</v>
       </c>
       <c r="C855" t="s">
-        <v>256</v>
+        <v>1229</v>
       </c>
       <c r="D855" t="s">
         <v>8</v>
@@ -91285,7 +91285,7 @@
         <v>0</v>
       </c>
       <c r="H855" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
@@ -91293,10 +91293,10 @@
         <v>5</v>
       </c>
       <c r="B856" t="s">
-        <v>1228</v>
+        <v>1638</v>
       </c>
       <c r="C856" t="s">
-        <v>1229</v>
+        <v>1639</v>
       </c>
       <c r="D856" t="s">
         <v>8</v>
@@ -91308,7 +91308,7 @@
         <v>0</v>
       </c>
       <c r="H856" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
@@ -91316,10 +91316,10 @@
         <v>5</v>
       </c>
       <c r="B857" t="s">
-        <v>1638</v>
+        <v>207</v>
       </c>
       <c r="C857" t="s">
-        <v>1639</v>
+        <v>208</v>
       </c>
       <c r="D857" t="s">
         <v>8</v>
@@ -91331,7 +91331,7 @@
         <v>0</v>
       </c>
       <c r="H857" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
@@ -91339,10 +91339,10 @@
         <v>5</v>
       </c>
       <c r="B858" t="s">
-        <v>207</v>
+        <v>2661</v>
       </c>
       <c r="C858" t="s">
-        <v>208</v>
+        <v>2662</v>
       </c>
       <c r="D858" t="s">
         <v>8</v>
@@ -91362,10 +91362,10 @@
         <v>5</v>
       </c>
       <c r="B859" t="s">
-        <v>2661</v>
+        <v>29</v>
       </c>
       <c r="C859" t="s">
-        <v>2662</v>
+        <v>30</v>
       </c>
       <c r="D859" t="s">
         <v>8</v>
@@ -91385,10 +91385,10 @@
         <v>5</v>
       </c>
       <c r="B860" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C860" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D860" t="s">
         <v>8</v>
@@ -91400,7 +91400,7 @@
         <v>0</v>
       </c>
       <c r="H860" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
@@ -91408,10 +91408,10 @@
         <v>5</v>
       </c>
       <c r="B861" t="s">
-        <v>31</v>
+        <v>2745</v>
       </c>
       <c r="C861" t="s">
-        <v>32</v>
+        <v>2746</v>
       </c>
       <c r="D861" t="s">
         <v>8</v>
@@ -91423,7 +91423,7 @@
         <v>0</v>
       </c>
       <c r="H861" t="s">
-        <v>6170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
@@ -91431,10 +91431,10 @@
         <v>5</v>
       </c>
       <c r="B862" t="s">
-        <v>2745</v>
+        <v>2725</v>
       </c>
       <c r="C862" t="s">
-        <v>2746</v>
+        <v>2726</v>
       </c>
       <c r="D862" t="s">
         <v>8</v>
@@ -91454,10 +91454,10 @@
         <v>5</v>
       </c>
       <c r="B863" t="s">
-        <v>2725</v>
+        <v>2727</v>
       </c>
       <c r="C863" t="s">
-        <v>2726</v>
+        <v>2728</v>
       </c>
       <c r="D863" t="s">
         <v>8</v>
@@ -91477,10 +91477,10 @@
         <v>5</v>
       </c>
       <c r="B864" t="s">
-        <v>2727</v>
+        <v>2695</v>
       </c>
       <c r="C864" t="s">
-        <v>2728</v>
+        <v>2696</v>
       </c>
       <c r="D864" t="s">
         <v>8</v>
@@ -91500,10 +91500,10 @@
         <v>5</v>
       </c>
       <c r="B865" t="s">
-        <v>2695</v>
+        <v>4782</v>
       </c>
       <c r="C865" t="s">
-        <v>2696</v>
+        <v>4783</v>
       </c>
       <c r="D865" t="s">
         <v>8</v>
@@ -91523,10 +91523,10 @@
         <v>5</v>
       </c>
       <c r="B866" t="s">
-        <v>4782</v>
+        <v>1693</v>
       </c>
       <c r="C866" t="s">
-        <v>4783</v>
+        <v>1694</v>
       </c>
       <c r="D866" t="s">
         <v>8</v>
@@ -91538,7 +91538,7 @@
         <v>0</v>
       </c>
       <c r="H866" t="s">
-        <v>13</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="867" spans="1:8" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18512,7 +18512,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-09-01 a 2026-09-26)</t>
+    <t>Ventas (2026-09-01 a 2026-09-27)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -20000,7 +20000,7 @@
         <v>41</v>
       </c>
       <c r="E64">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -21156,7 +21156,7 @@
         <v>18</v>
       </c>
       <c r="E132">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -22465,7 +22465,7 @@
         <v>423</v>
       </c>
       <c r="E209">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -22533,7 +22533,7 @@
         <v>198</v>
       </c>
       <c r="E213">
-        <v>32</v>
+        <v>248</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -26035,7 +26035,7 @@
         <v>18</v>
       </c>
       <c r="E419">
-        <v>240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -27939,7 +27939,7 @@
         <v>8</v>
       </c>
       <c r="E531">
-        <v>84</v>
+        <v>48</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -28143,7 +28143,7 @@
         <v>13</v>
       </c>
       <c r="E543">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -28381,7 +28381,7 @@
         <v>8</v>
       </c>
       <c r="E557">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -29299,7 +29299,7 @@
         <v>61</v>
       </c>
       <c r="E611">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
@@ -29316,7 +29316,7 @@
         <v>8</v>
       </c>
       <c r="E612">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
@@ -29520,7 +29520,7 @@
         <v>85</v>
       </c>
       <c r="E624">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
@@ -29588,7 +29588,7 @@
         <v>423</v>
       </c>
       <c r="E628">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -29622,7 +29622,7 @@
         <v>423</v>
       </c>
       <c r="E630">
-        <v>288</v>
+        <v>278</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -29673,7 +29673,7 @@
         <v>423</v>
       </c>
       <c r="E633">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -29894,7 +29894,7 @@
         <v>13</v>
       </c>
       <c r="E646">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -29928,7 +29928,7 @@
         <v>18</v>
       </c>
       <c r="E648">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -30591,7 +30591,7 @@
         <v>18</v>
       </c>
       <c r="E687">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
@@ -31509,7 +31509,7 @@
         <v>18</v>
       </c>
       <c r="E741">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.25">
@@ -31662,7 +31662,7 @@
         <v>8</v>
       </c>
       <c r="E750">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
@@ -31951,7 +31951,7 @@
         <v>61</v>
       </c>
       <c r="E767">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="768" spans="1:5" x14ac:dyDescent="0.25">
@@ -31968,7 +31968,7 @@
         <v>61</v>
       </c>
       <c r="E768">
-        <v>149</v>
+        <v>131</v>
       </c>
     </row>
     <row r="769" spans="1:5" x14ac:dyDescent="0.25">
@@ -32002,7 +32002,7 @@
         <v>18</v>
       </c>
       <c r="E770">
-        <v>324</v>
+        <v>252</v>
       </c>
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.25">
@@ -33039,7 +33039,7 @@
         <v>8</v>
       </c>
       <c r="E831">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.25">
@@ -33294,7 +33294,7 @@
         <v>8</v>
       </c>
       <c r="E846">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.25">
@@ -33753,7 +33753,7 @@
         <v>61</v>
       </c>
       <c r="E873">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="874" spans="1:5" x14ac:dyDescent="0.25">
@@ -33974,7 +33974,7 @@
         <v>85</v>
       </c>
       <c r="E886">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.25">
@@ -34025,7 +34025,7 @@
         <v>85</v>
       </c>
       <c r="E889">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890" spans="1:5" x14ac:dyDescent="0.25">
@@ -34535,7 +34535,7 @@
         <v>8</v>
       </c>
       <c r="E919">
-        <v>264</v>
+        <v>228</v>
       </c>
     </row>
     <row r="920" spans="1:5" x14ac:dyDescent="0.25">
@@ -34841,7 +34841,7 @@
         <v>18</v>
       </c>
       <c r="E937">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="938" spans="1:5" x14ac:dyDescent="0.25">
@@ -35708,7 +35708,7 @@
         <v>18</v>
       </c>
       <c r="E988">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.25">
@@ -35725,7 +35725,7 @@
         <v>85</v>
       </c>
       <c r="E989">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="990" spans="1:5" x14ac:dyDescent="0.25">
@@ -37476,7 +37476,7 @@
         <v>18</v>
       </c>
       <c r="E1092">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1093" spans="1:5" x14ac:dyDescent="0.25">
@@ -37952,7 +37952,7 @@
         <v>198</v>
       </c>
       <c r="E1120">
-        <v>336</v>
+        <v>264</v>
       </c>
     </row>
     <row r="1121" spans="1:5" x14ac:dyDescent="0.25">
@@ -41879,7 +41879,7 @@
         <v>8</v>
       </c>
       <c r="E1351">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1352" spans="1:5" x14ac:dyDescent="0.25">
@@ -43205,7 +43205,7 @@
         <v>18</v>
       </c>
       <c r="E1429">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1430" spans="1:5" x14ac:dyDescent="0.25">
@@ -44650,7 +44650,7 @@
         <v>61</v>
       </c>
       <c r="E1514">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1515" spans="1:5" x14ac:dyDescent="0.25">
@@ -49206,7 +49206,7 @@
         <v>61</v>
       </c>
       <c r="E1782">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1783" spans="1:5" x14ac:dyDescent="0.25">
@@ -49410,7 +49410,7 @@
         <v>61</v>
       </c>
       <c r="E1794">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1795" spans="1:5" x14ac:dyDescent="0.25">
@@ -49716,7 +49716,7 @@
         <v>41</v>
       </c>
       <c r="E1812">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1813" spans="1:5" x14ac:dyDescent="0.25">
@@ -51246,7 +51246,7 @@
         <v>61</v>
       </c>
       <c r="E1902">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1903" spans="1:5" x14ac:dyDescent="0.25">
@@ -52504,7 +52504,7 @@
         <v>61</v>
       </c>
       <c r="E1976">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1977" spans="1:5" x14ac:dyDescent="0.25">
@@ -53235,7 +53235,7 @@
         <v>61</v>
       </c>
       <c r="E2019">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2020" spans="1:5" x14ac:dyDescent="0.25">
@@ -53252,7 +53252,7 @@
         <v>61</v>
       </c>
       <c r="E2020">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2021" spans="1:5" x14ac:dyDescent="0.25">
@@ -56363,7 +56363,7 @@
         <v>8</v>
       </c>
       <c r="E2203">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2204" spans="1:5" x14ac:dyDescent="0.25">
@@ -59559,7 +59559,7 @@
         <v>8</v>
       </c>
       <c r="E2391">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2392" spans="1:5" x14ac:dyDescent="0.25">
@@ -62500,7 +62500,7 @@
         <v>8</v>
       </c>
       <c r="E2564">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2565" spans="1:5" x14ac:dyDescent="0.25">
@@ -65016,7 +65016,7 @@
         <v>61</v>
       </c>
       <c r="E2712">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2713" spans="1:5" x14ac:dyDescent="0.25">
@@ -65033,7 +65033,7 @@
         <v>61</v>
       </c>
       <c r="E2713">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2714" spans="1:5" x14ac:dyDescent="0.25">
@@ -65050,7 +65050,7 @@
         <v>8</v>
       </c>
       <c r="E2714">
-        <v>192</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2715" spans="1:5" x14ac:dyDescent="0.25">
@@ -66053,7 +66053,7 @@
         <v>8</v>
       </c>
       <c r="E2773">
-        <v>360</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2774" spans="1:5" x14ac:dyDescent="0.25">
@@ -67498,7 +67498,7 @@
         <v>61</v>
       </c>
       <c r="E2858">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="2859" spans="1:5" x14ac:dyDescent="0.25">
@@ -68484,7 +68484,7 @@
         <v>18</v>
       </c>
       <c r="E2916">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2917" spans="1:5" x14ac:dyDescent="0.25">
@@ -68858,7 +68858,7 @@
         <v>85</v>
       </c>
       <c r="E2938">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2939" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18512,7 +18512,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-01)</t>
+    <t>Ventas (2026-10-01 a 2026-10-02)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -29605,7 +29605,7 @@
         <v>423</v>
       </c>
       <c r="E629">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
@@ -31662,7 +31662,7 @@
         <v>8</v>
       </c>
       <c r="E750">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
@@ -35062,7 +35062,7 @@
         <v>13</v>
       </c>
       <c r="E950">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="951" spans="1:5" x14ac:dyDescent="0.25">
@@ -41267,7 +41267,7 @@
         <v>61</v>
       </c>
       <c r="E1315">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1316" spans="1:5" x14ac:dyDescent="0.25">
@@ -44650,7 +44650,7 @@
         <v>61</v>
       </c>
       <c r="E1514">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1515" spans="1:5" x14ac:dyDescent="0.25">
@@ -46299,7 +46299,7 @@
         <v>48</v>
       </c>
       <c r="E1611">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1612" spans="1:5" x14ac:dyDescent="0.25">
@@ -47200,7 +47200,7 @@
         <v>41</v>
       </c>
       <c r="E1664">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1665" spans="1:5" x14ac:dyDescent="0.25">
@@ -51280,7 +51280,7 @@
         <v>61</v>
       </c>
       <c r="E1904">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1905" spans="1:5" x14ac:dyDescent="0.25">
@@ -51552,7 +51552,7 @@
         <v>61</v>
       </c>
       <c r="E1920">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="1921" spans="1:5" x14ac:dyDescent="0.25">
@@ -54493,7 +54493,7 @@
         <v>61</v>
       </c>
       <c r="E2093">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2094" spans="1:5" x14ac:dyDescent="0.25">
@@ -65169,7 +65169,7 @@
         <v>61</v>
       </c>
       <c r="E2721">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2722" spans="1:5" x14ac:dyDescent="0.25">
@@ -66053,7 +66053,7 @@
         <v>8</v>
       </c>
       <c r="E2773">
-        <v>282</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2774" spans="1:5" x14ac:dyDescent="0.25">
@@ -67498,7 +67498,7 @@
         <v>61</v>
       </c>
       <c r="E2858">
-        <v>690</v>
+        <v>678</v>
       </c>
     </row>
     <row r="2859" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18512,7 +18512,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-02)</t>
+    <t>Ventas (2026-10-01 a 2026-10-03)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -22533,7 +22533,7 @@
         <v>198</v>
       </c>
       <c r="E213">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -25984,7 +25984,7 @@
         <v>8</v>
       </c>
       <c r="E416">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -26647,7 +26647,7 @@
         <v>88</v>
       </c>
       <c r="E455">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
@@ -29316,7 +29316,7 @@
         <v>8</v>
       </c>
       <c r="E612">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
@@ -29622,7 +29622,7 @@
         <v>423</v>
       </c>
       <c r="E630">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -33141,7 +33141,7 @@
         <v>18</v>
       </c>
       <c r="E837">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="838" spans="1:5" x14ac:dyDescent="0.25">
@@ -33260,7 +33260,7 @@
         <v>8</v>
       </c>
       <c r="E844">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.25">
@@ -33277,7 +33277,7 @@
         <v>13</v>
       </c>
       <c r="E845">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.25">
@@ -33974,7 +33974,7 @@
         <v>85</v>
       </c>
       <c r="E886">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.25">
@@ -35266,7 +35266,7 @@
         <v>88</v>
       </c>
       <c r="E962">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="963" spans="1:5" x14ac:dyDescent="0.25">
@@ -35300,7 +35300,7 @@
         <v>88</v>
       </c>
       <c r="E964">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="965" spans="1:5" x14ac:dyDescent="0.25">
@@ -35317,7 +35317,7 @@
         <v>88</v>
       </c>
       <c r="E965">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="966" spans="1:5" x14ac:dyDescent="0.25">
@@ -35334,7 +35334,7 @@
         <v>88</v>
       </c>
       <c r="E966">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="967" spans="1:5" x14ac:dyDescent="0.25">
@@ -35572,7 +35572,7 @@
         <v>423</v>
       </c>
       <c r="E980">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="981" spans="1:5" x14ac:dyDescent="0.25">
@@ -49716,7 +49716,7 @@
         <v>41</v>
       </c>
       <c r="E1812">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1813" spans="1:5" x14ac:dyDescent="0.25">
@@ -50617,7 +50617,7 @@
         <v>85</v>
       </c>
       <c r="E1865">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1866" spans="1:5" x14ac:dyDescent="0.25">
@@ -51552,7 +51552,7 @@
         <v>61</v>
       </c>
       <c r="E1920">
-        <v>285</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1921" spans="1:5" x14ac:dyDescent="0.25">
@@ -52385,7 +52385,7 @@
         <v>423</v>
       </c>
       <c r="E1969">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="1970" spans="1:5" x14ac:dyDescent="0.25">
@@ -56363,7 +56363,7 @@
         <v>8</v>
       </c>
       <c r="E2203">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2204" spans="1:5" x14ac:dyDescent="0.25">
@@ -59559,7 +59559,7 @@
         <v>8</v>
       </c>
       <c r="E2391">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2392" spans="1:5" x14ac:dyDescent="0.25">
@@ -63163,7 +63163,7 @@
         <v>8</v>
       </c>
       <c r="E2603">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2604" spans="1:5" x14ac:dyDescent="0.25">
@@ -65288,7 +65288,7 @@
         <v>8</v>
       </c>
       <c r="E2728">
-        <v>76</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2729" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18512,7 +18512,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-03)</t>
+    <t>Ventas (2026-10-01 a 2026-10-04)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -22431,7 +22431,7 @@
         <v>423</v>
       </c>
       <c r="E207">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -22448,7 +22448,7 @@
         <v>423</v>
       </c>
       <c r="E208">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -22465,7 +22465,7 @@
         <v>423</v>
       </c>
       <c r="E209">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
@@ -22533,7 +22533,7 @@
         <v>198</v>
       </c>
       <c r="E213">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -25984,7 +25984,7 @@
         <v>8</v>
       </c>
       <c r="E416">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -26035,7 +26035,7 @@
         <v>18</v>
       </c>
       <c r="E419">
-        <v>156</v>
+        <v>120</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -29588,7 +29588,7 @@
         <v>423</v>
       </c>
       <c r="E628">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -29673,7 +29673,7 @@
         <v>423</v>
       </c>
       <c r="E633">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -29707,7 +29707,7 @@
         <v>423</v>
       </c>
       <c r="E635">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -29928,7 +29928,7 @@
         <v>18</v>
       </c>
       <c r="E648">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -31390,7 +31390,7 @@
         <v>85</v>
       </c>
       <c r="E734">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -31509,7 +31509,7 @@
         <v>18</v>
       </c>
       <c r="E741">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.25">
@@ -31968,7 +31968,7 @@
         <v>61</v>
       </c>
       <c r="E768">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="769" spans="1:5" x14ac:dyDescent="0.25">
@@ -32002,7 +32002,7 @@
         <v>18</v>
       </c>
       <c r="E770">
-        <v>252</v>
+        <v>216</v>
       </c>
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.25">
@@ -33039,7 +33039,7 @@
         <v>8</v>
       </c>
       <c r="E831">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.25">
@@ -33668,7 +33668,7 @@
         <v>61</v>
       </c>
       <c r="E868">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.25">
@@ -33753,7 +33753,7 @@
         <v>61</v>
       </c>
       <c r="E873">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="874" spans="1:5" x14ac:dyDescent="0.25">
@@ -35572,7 +35572,7 @@
         <v>423</v>
       </c>
       <c r="E980">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="981" spans="1:5" x14ac:dyDescent="0.25">
@@ -35708,7 +35708,7 @@
         <v>18</v>
       </c>
       <c r="E988">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.25">
@@ -36235,7 +36235,7 @@
         <v>198</v>
       </c>
       <c r="E1019">
-        <v>144</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1020" spans="1:5" x14ac:dyDescent="0.25">
@@ -36252,7 +36252,7 @@
         <v>198</v>
       </c>
       <c r="E1020">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1021" spans="1:5" x14ac:dyDescent="0.25">
@@ -37952,7 +37952,7 @@
         <v>198</v>
       </c>
       <c r="E1120">
-        <v>144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1121" spans="1:5" x14ac:dyDescent="0.25">
@@ -38785,7 +38785,7 @@
         <v>8</v>
       </c>
       <c r="E1169">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1170" spans="1:5" x14ac:dyDescent="0.25">
@@ -49410,7 +49410,7 @@
         <v>61</v>
       </c>
       <c r="E1794">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1795" spans="1:5" x14ac:dyDescent="0.25">
@@ -52385,7 +52385,7 @@
         <v>423</v>
       </c>
       <c r="E1969">
-        <v>812</v>
+        <v>805</v>
       </c>
     </row>
     <row r="1970" spans="1:5" x14ac:dyDescent="0.25">
@@ -61922,7 +61922,7 @@
         <v>18</v>
       </c>
       <c r="E2530">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2531" spans="1:5" x14ac:dyDescent="0.25">
@@ -65118,7 +65118,7 @@
         <v>61</v>
       </c>
       <c r="E2718">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2719" spans="1:5" x14ac:dyDescent="0.25">
@@ -65237,7 +65237,7 @@
         <v>8</v>
       </c>
       <c r="E2725">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2726" spans="1:5" x14ac:dyDescent="0.25">
@@ -67498,7 +67498,7 @@
         <v>61</v>
       </c>
       <c r="E2858">
-        <v>678</v>
+        <v>666</v>
       </c>
     </row>
     <row r="2859" spans="1:5" x14ac:dyDescent="0.25">
@@ -68399,7 +68399,7 @@
         <v>85</v>
       </c>
       <c r="E2911">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2912" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18512,7 +18512,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-05)</t>
+    <t>Ventas (2026-10-01 a 2026-10-06)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -22533,7 +22533,7 @@
         <v>198</v>
       </c>
       <c r="E213">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -24420,7 +24420,7 @@
         <v>18</v>
       </c>
       <c r="E324">
-        <v>192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -29894,7 +29894,7 @@
         <v>13</v>
       </c>
       <c r="E646">
-        <v>215</v>
+        <v>179</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -30676,7 +30676,7 @@
         <v>61</v>
       </c>
       <c r="E692">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
@@ -31662,7 +31662,7 @@
         <v>8</v>
       </c>
       <c r="E750">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
@@ -32376,7 +32376,7 @@
         <v>61</v>
       </c>
       <c r="E792">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="793" spans="1:5" x14ac:dyDescent="0.25">
@@ -33294,7 +33294,7 @@
         <v>8</v>
       </c>
       <c r="E846">
-        <v>84</v>
+        <v>36</v>
       </c>
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.25">
@@ -33668,7 +33668,7 @@
         <v>61</v>
       </c>
       <c r="E868">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.25">
@@ -33906,7 +33906,7 @@
         <v>8</v>
       </c>
       <c r="E882">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.25">
@@ -34535,7 +34535,7 @@
         <v>8</v>
       </c>
       <c r="E919">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="920" spans="1:5" x14ac:dyDescent="0.25">
@@ -35708,7 +35708,7 @@
         <v>18</v>
       </c>
       <c r="E988">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.25">
@@ -35742,7 +35742,7 @@
         <v>8</v>
       </c>
       <c r="E990">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="991" spans="1:5" x14ac:dyDescent="0.25">
@@ -37935,7 +37935,7 @@
         <v>198</v>
       </c>
       <c r="E1119">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1120" spans="1:5" x14ac:dyDescent="0.25">
@@ -38275,7 +38275,7 @@
         <v>198</v>
       </c>
       <c r="E1139">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1140" spans="1:5" x14ac:dyDescent="0.25">
@@ -38292,7 +38292,7 @@
         <v>198</v>
       </c>
       <c r="E1140">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1141" spans="1:5" x14ac:dyDescent="0.25">
@@ -38343,7 +38343,7 @@
         <v>198</v>
       </c>
       <c r="E1143">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1144" spans="1:5" x14ac:dyDescent="0.25">
@@ -38479,7 +38479,7 @@
         <v>198</v>
       </c>
       <c r="E1151">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1152" spans="1:5" x14ac:dyDescent="0.25">
@@ -38717,7 +38717,7 @@
         <v>198</v>
       </c>
       <c r="E1165">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1166" spans="1:5" x14ac:dyDescent="0.25">
@@ -38785,7 +38785,7 @@
         <v>8</v>
       </c>
       <c r="E1169">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1170" spans="1:5" x14ac:dyDescent="0.25">
@@ -39329,7 +39329,7 @@
         <v>198</v>
       </c>
       <c r="E1201">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1202" spans="1:5" x14ac:dyDescent="0.25">
@@ -39363,7 +39363,7 @@
         <v>198</v>
       </c>
       <c r="E1203">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1204" spans="1:5" x14ac:dyDescent="0.25">
@@ -39431,7 +39431,7 @@
         <v>198</v>
       </c>
       <c r="E1207">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1208" spans="1:5" x14ac:dyDescent="0.25">
@@ -41267,7 +41267,7 @@
         <v>61</v>
       </c>
       <c r="E1315">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1316" spans="1:5" x14ac:dyDescent="0.25">
@@ -41454,7 +41454,7 @@
         <v>8</v>
       </c>
       <c r="E1326">
-        <v>308</v>
+        <v>272</v>
       </c>
     </row>
     <row r="1327" spans="1:5" x14ac:dyDescent="0.25">
@@ -41658,7 +41658,7 @@
         <v>61</v>
       </c>
       <c r="E1338">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1339" spans="1:5" x14ac:dyDescent="0.25">
@@ -47251,7 +47251,7 @@
         <v>61</v>
       </c>
       <c r="E1667">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1668" spans="1:5" x14ac:dyDescent="0.25">
@@ -47948,7 +47948,7 @@
         <v>41</v>
       </c>
       <c r="E1708">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1709" spans="1:5" x14ac:dyDescent="0.25">
@@ -51110,7 +51110,7 @@
         <v>61</v>
       </c>
       <c r="E1894">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1895" spans="1:5" x14ac:dyDescent="0.25">
@@ -51552,7 +51552,7 @@
         <v>61</v>
       </c>
       <c r="E1920">
-        <v>273</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1921" spans="1:5" x14ac:dyDescent="0.25">
@@ -53235,7 +53235,7 @@
         <v>61</v>
       </c>
       <c r="E2019">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2020" spans="1:5" x14ac:dyDescent="0.25">
@@ -53252,7 +53252,7 @@
         <v>61</v>
       </c>
       <c r="E2020">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2021" spans="1:5" x14ac:dyDescent="0.25">
@@ -53269,7 +53269,7 @@
         <v>61</v>
       </c>
       <c r="E2021">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2022" spans="1:5" x14ac:dyDescent="0.25">
@@ -53286,7 +53286,7 @@
         <v>61</v>
       </c>
       <c r="E2022">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2023" spans="1:5" x14ac:dyDescent="0.25">
@@ -56363,7 +56363,7 @@
         <v>8</v>
       </c>
       <c r="E2203">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2204" spans="1:5" x14ac:dyDescent="0.25">
@@ -62500,7 +62500,7 @@
         <v>8</v>
       </c>
       <c r="E2564">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2565" spans="1:5" x14ac:dyDescent="0.25">
@@ -65016,7 +65016,7 @@
         <v>61</v>
       </c>
       <c r="E2712">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2713" spans="1:5" x14ac:dyDescent="0.25">
@@ -65118,7 +65118,7 @@
         <v>61</v>
       </c>
       <c r="E2718">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2719" spans="1:5" x14ac:dyDescent="0.25">
@@ -65169,7 +65169,7 @@
         <v>61</v>
       </c>
       <c r="E2721">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2722" spans="1:5" x14ac:dyDescent="0.25">
@@ -65237,7 +65237,7 @@
         <v>8</v>
       </c>
       <c r="E2725">
-        <v>192</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2726" spans="1:5" x14ac:dyDescent="0.25">
@@ -67498,7 +67498,7 @@
         <v>61</v>
       </c>
       <c r="E2858">
-        <v>630</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2859" spans="1:5" x14ac:dyDescent="0.25">
@@ -68858,7 +68858,7 @@
         <v>85</v>
       </c>
       <c r="E2938">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2939" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18518,7 +18518,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-15)</t>
+    <t>Ventas (2026-10-01 a 2026-10-16)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -29900,7 +29900,7 @@
         <v>13</v>
       </c>
       <c r="E646">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -31056,7 +31056,7 @@
         <v>85</v>
       </c>
       <c r="E714">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.25">
@@ -31668,7 +31668,7 @@
         <v>8</v>
       </c>
       <c r="E750">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
@@ -31974,7 +31974,7 @@
         <v>61</v>
       </c>
       <c r="E768">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="769" spans="1:5" x14ac:dyDescent="0.25">
@@ -33266,7 +33266,7 @@
         <v>8</v>
       </c>
       <c r="E844">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.25">
@@ -35085,7 +35085,7 @@
         <v>13</v>
       </c>
       <c r="E951">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="952" spans="1:5" x14ac:dyDescent="0.25">
@@ -35731,7 +35731,7 @@
         <v>18</v>
       </c>
       <c r="E989">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="990" spans="1:5" x14ac:dyDescent="0.25">
@@ -37499,7 +37499,7 @@
         <v>18</v>
       </c>
       <c r="E1093">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1094" spans="1:5" x14ac:dyDescent="0.25">
@@ -44673,7 +44673,7 @@
         <v>61</v>
       </c>
       <c r="E1515">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1516" spans="1:5" x14ac:dyDescent="0.25">
@@ -51303,7 +51303,7 @@
         <v>61</v>
       </c>
       <c r="E1905">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1906" spans="1:5" x14ac:dyDescent="0.25">
@@ -54516,7 +54516,7 @@
         <v>61</v>
       </c>
       <c r="E2094">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2095" spans="1:5" x14ac:dyDescent="0.25">
@@ -63373,7 +63373,7 @@
         <v>8</v>
       </c>
       <c r="E2615">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2616" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18698,7 +18698,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-20)</t>
+    <t>Ventas (2026-10-01 a 2026-10-21)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -20645,7 +20645,7 @@
         <v>8</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -26221,7 +26221,7 @@
         <v>18</v>
       </c>
       <c r="E419">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -29876,7 +29876,7 @@
         <v>18</v>
       </c>
       <c r="E634">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -30080,7 +30080,7 @@
         <v>13</v>
       </c>
       <c r="E646">
-        <v>161</v>
+        <v>89</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -31049,7 +31049,7 @@
         <v>85</v>
       </c>
       <c r="E703">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.25">
@@ -31151,7 +31151,7 @@
         <v>85</v>
       </c>
       <c r="E709">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.25">
@@ -31372,7 +31372,7 @@
         <v>85</v>
       </c>
       <c r="E722">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.25">
@@ -31389,7 +31389,7 @@
         <v>18</v>
       </c>
       <c r="E723">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
@@ -31576,7 +31576,7 @@
         <v>85</v>
       </c>
       <c r="E734">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -31848,7 +31848,7 @@
         <v>8</v>
       </c>
       <c r="E750">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
@@ -32188,7 +32188,7 @@
         <v>18</v>
       </c>
       <c r="E770">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.25">
@@ -32732,7 +32732,7 @@
         <v>41</v>
       </c>
       <c r="E802">
-        <v>12</v>
+        <v>65</v>
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.25">
@@ -32953,7 +32953,7 @@
         <v>8</v>
       </c>
       <c r="E815">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.25">
@@ -33871,7 +33871,7 @@
         <v>61</v>
       </c>
       <c r="E869">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.25">
@@ -38614,7 +38614,7 @@
         <v>198</v>
       </c>
       <c r="E1148">
-        <v>264</v>
+        <v>216</v>
       </c>
     </row>
     <row r="1149" spans="1:5" x14ac:dyDescent="0.25">
@@ -43935,7 +43935,7 @@
         <v>18</v>
       </c>
       <c r="E1461">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1462" spans="1:5" x14ac:dyDescent="0.25">
@@ -50378,7 +50378,7 @@
         <v>41</v>
       </c>
       <c r="E1840">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1841" spans="1:5" x14ac:dyDescent="0.25">
@@ -52214,7 +52214,7 @@
         <v>61</v>
       </c>
       <c r="E1948">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="1949" spans="1:5" x14ac:dyDescent="0.25">
@@ -53948,7 +53948,7 @@
         <v>61</v>
       </c>
       <c r="E2050">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2051" spans="1:5" x14ac:dyDescent="0.25">
@@ -54407,7 +54407,7 @@
         <v>18</v>
       </c>
       <c r="E2077">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2078" spans="1:5" x14ac:dyDescent="0.25">
@@ -62584,7 +62584,7 @@
         <v>126</v>
       </c>
       <c r="E2558">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2559" spans="1:5" x14ac:dyDescent="0.25">
@@ -65950,7 +65950,7 @@
         <v>8</v>
       </c>
       <c r="E2756">
-        <v>108</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2757" spans="1:5" x14ac:dyDescent="0.25">
@@ -66766,7 +66766,7 @@
         <v>8</v>
       </c>
       <c r="E2804">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2805" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18698,7 +18698,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-22)</t>
+    <t>Ventas (2026-10-01 a 2026-10-23)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -20186,7 +20186,7 @@
         <v>41</v>
       </c>
       <c r="E64">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -21342,7 +21342,7 @@
         <v>18</v>
       </c>
       <c r="E132">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -27955,7 +27955,7 @@
         <v>61</v>
       </c>
       <c r="E521">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
@@ -28125,7 +28125,7 @@
         <v>8</v>
       </c>
       <c r="E531">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -29502,7 +29502,7 @@
         <v>8</v>
       </c>
       <c r="E612">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
@@ -29893,7 +29893,7 @@
         <v>423</v>
       </c>
       <c r="E635">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -30811,7 +30811,7 @@
         <v>85</v>
       </c>
       <c r="E689">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
@@ -31372,7 +31372,7 @@
         <v>85</v>
       </c>
       <c r="E722">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.25">
@@ -31389,7 +31389,7 @@
         <v>18</v>
       </c>
       <c r="E723">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
@@ -31576,7 +31576,7 @@
         <v>85</v>
       </c>
       <c r="E734">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -31729,7 +31729,7 @@
         <v>18</v>
       </c>
       <c r="E743">
-        <v>228</v>
+        <v>216</v>
       </c>
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.25">
@@ -33225,7 +33225,7 @@
         <v>8</v>
       </c>
       <c r="E831">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.25">
@@ -34738,7 +34738,7 @@
         <v>8</v>
       </c>
       <c r="E920">
-        <v>144</v>
+        <v>96</v>
       </c>
     </row>
     <row r="921" spans="1:5" x14ac:dyDescent="0.25">
@@ -35894,7 +35894,7 @@
         <v>8</v>
       </c>
       <c r="E988">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.25">
@@ -42507,7 +42507,7 @@
         <v>41</v>
       </c>
       <c r="E1377">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1378" spans="1:5" x14ac:dyDescent="0.25">
@@ -47726,7 +47726,7 @@
         <v>41</v>
       </c>
       <c r="E1684">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1685" spans="1:5" x14ac:dyDescent="0.25">
@@ -53914,7 +53914,7 @@
         <v>61</v>
       </c>
       <c r="E2048">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2049" spans="1:5" x14ac:dyDescent="0.25">
@@ -53931,7 +53931,7 @@
         <v>61</v>
       </c>
       <c r="E2049">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2050" spans="1:5" x14ac:dyDescent="0.25">
@@ -55189,7 +55189,7 @@
         <v>61</v>
       </c>
       <c r="E2123">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2124" spans="1:5" x14ac:dyDescent="0.25">
@@ -62584,7 +62584,7 @@
         <v>126</v>
       </c>
       <c r="E2558">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2559" spans="1:5" x14ac:dyDescent="0.25">
@@ -63230,7 +63230,7 @@
         <v>8</v>
       </c>
       <c r="E2596">
-        <v>228</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2597" spans="1:5" x14ac:dyDescent="0.25">
@@ -63757,7 +63757,7 @@
         <v>61</v>
       </c>
       <c r="E2627">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2628" spans="1:5" x14ac:dyDescent="0.25">
@@ -65950,7 +65950,7 @@
         <v>8</v>
       </c>
       <c r="E2756">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2757" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18698,7 +18698,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-23)</t>
+    <t>Ventas (2026-10-01 a 2026-10-24)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -19863,7 +19863,7 @@
         <v>100</v>
       </c>
       <c r="E45">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -19931,7 +19931,7 @@
         <v>100</v>
       </c>
       <c r="E49">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -30080,7 +30080,7 @@
         <v>13</v>
       </c>
       <c r="E646">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -33871,7 +33871,7 @@
         <v>61</v>
       </c>
       <c r="E869">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.25">
@@ -43595,7 +43595,7 @@
         <v>126</v>
       </c>
       <c r="E1441">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1442" spans="1:5" x14ac:dyDescent="0.25">
@@ -45312,7 +45312,7 @@
         <v>61</v>
       </c>
       <c r="E1542">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1543" spans="1:5" x14ac:dyDescent="0.25">
@@ -45669,7 +45669,7 @@
         <v>61</v>
       </c>
       <c r="E1563">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1564" spans="1:5" x14ac:dyDescent="0.25">
@@ -49868,7 +49868,7 @@
         <v>61</v>
       </c>
       <c r="E1810">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1811" spans="1:5" x14ac:dyDescent="0.25">
@@ -51942,7 +51942,7 @@
         <v>61</v>
       </c>
       <c r="E1932">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1933" spans="1:5" x14ac:dyDescent="0.25">
@@ -55036,7 +55036,7 @@
         <v>61</v>
       </c>
       <c r="E2114">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2115" spans="1:5" x14ac:dyDescent="0.25">
@@ -55512,7 +55512,7 @@
         <v>61</v>
       </c>
       <c r="E2142">
-        <v>197</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2143" spans="1:5" x14ac:dyDescent="0.25">
@@ -69571,7 +69571,7 @@
         <v>85</v>
       </c>
       <c r="E2969">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2970" spans="1:5" x14ac:dyDescent="0.25">
@@ -71101,7 +71101,7 @@
         <v>8</v>
       </c>
       <c r="E3059">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3060" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18698,7 +18698,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-25)</t>
+    <t>Ventas (2026-10-01 a 2026-10-26)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -26204,7 +26204,7 @@
         <v>61</v>
       </c>
       <c r="E418">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -27870,7 +27870,7 @@
         <v>61</v>
       </c>
       <c r="E516">
-        <v>65</v>
+        <v>29</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
@@ -28125,7 +28125,7 @@
         <v>8</v>
       </c>
       <c r="E531">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -30080,7 +30080,7 @@
         <v>13</v>
       </c>
       <c r="E646">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -31729,7 +31729,7 @@
         <v>18</v>
       </c>
       <c r="E743">
-        <v>216</v>
+        <v>180</v>
       </c>
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.25">
@@ -32936,7 +32936,7 @@
         <v>8</v>
       </c>
       <c r="E814">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="815" spans="1:5" x14ac:dyDescent="0.25">
@@ -34738,7 +34738,7 @@
         <v>8</v>
       </c>
       <c r="E920">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="921" spans="1:5" x14ac:dyDescent="0.25">
@@ -35265,7 +35265,7 @@
         <v>13</v>
       </c>
       <c r="E951">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="952" spans="1:5" x14ac:dyDescent="0.25">
@@ -35894,7 +35894,7 @@
         <v>8</v>
       </c>
       <c r="E988">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.25">
@@ -35911,7 +35911,7 @@
         <v>18</v>
       </c>
       <c r="E989">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="990" spans="1:5" x14ac:dyDescent="0.25">
@@ -37390,7 +37390,7 @@
         <v>13</v>
       </c>
       <c r="E1076">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1077" spans="1:5" x14ac:dyDescent="0.25">
@@ -37407,7 +37407,7 @@
         <v>198</v>
       </c>
       <c r="E1077">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1078" spans="1:5" x14ac:dyDescent="0.25">
@@ -37424,7 +37424,7 @@
         <v>198</v>
       </c>
       <c r="E1078">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1079" spans="1:5" x14ac:dyDescent="0.25">
@@ -37441,7 +37441,7 @@
         <v>198</v>
       </c>
       <c r="E1079">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1080" spans="1:5" x14ac:dyDescent="0.25">
@@ -37458,7 +37458,7 @@
         <v>198</v>
       </c>
       <c r="E1080">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1081" spans="1:5" x14ac:dyDescent="0.25">
@@ -38614,7 +38614,7 @@
         <v>198</v>
       </c>
       <c r="E1148">
-        <v>216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1149" spans="1:5" x14ac:dyDescent="0.25">
@@ -42116,7 +42116,7 @@
         <v>8</v>
       </c>
       <c r="E1354">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1355" spans="1:5" x14ac:dyDescent="0.25">
@@ -42320,7 +42320,7 @@
         <v>61</v>
       </c>
       <c r="E1366">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1367" spans="1:5" x14ac:dyDescent="0.25">
@@ -45244,7 +45244,7 @@
         <v>18</v>
       </c>
       <c r="E1538">
-        <v>113</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1539" spans="1:5" x14ac:dyDescent="0.25">
@@ -45312,7 +45312,7 @@
         <v>61</v>
       </c>
       <c r="E1542">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1543" spans="1:5" x14ac:dyDescent="0.25">
@@ -52588,7 +52588,7 @@
         <v>61</v>
       </c>
       <c r="E1970">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1971" spans="1:5" x14ac:dyDescent="0.25">
@@ -57059,7 +57059,7 @@
         <v>8</v>
       </c>
       <c r="E2233">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2234" spans="1:5" x14ac:dyDescent="0.25">
@@ -63213,7 +63213,7 @@
         <v>8</v>
       </c>
       <c r="E2595">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2596" spans="1:5" x14ac:dyDescent="0.25">
@@ -63230,7 +63230,7 @@
         <v>8</v>
       </c>
       <c r="E2596">
-        <v>204</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2597" spans="1:5" x14ac:dyDescent="0.25">
@@ -64063,7 +64063,7 @@
         <v>8</v>
       </c>
       <c r="E2645">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2646" spans="1:5" x14ac:dyDescent="0.25">
@@ -65950,7 +65950,7 @@
         <v>8</v>
       </c>
       <c r="E2756">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2757" spans="1:5" x14ac:dyDescent="0.25">

--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18770,7 +18770,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-10-01 a 2026-10-29)</t>
+    <t>Ventas (2026-10-01 a 2026-10-30)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -26293,7 +26293,7 @@
         <v>18</v>
       </c>
       <c r="E419">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -30271,7 +30271,7 @@
         <v>18</v>
       </c>
       <c r="E653">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
@@ -42154,7 +42154,7 @@
         <v>126</v>
       </c>
       <c r="E1352">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1353" spans="1:5" x14ac:dyDescent="0.25">
@@ -52184,7 +52184,7 @@
         <v>61</v>
       </c>
       <c r="E1942">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1943" spans="1:5" x14ac:dyDescent="0.25">
